--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:32</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:32</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:32</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:32</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:32</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55894</v>
+        <v>55887</v>
       </c>
       <c r="F9" t="n">
         <v>0.0533</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7022</v>
+        <v>7023</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6384</v>
+        <v>6385</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:40</t>
+          <t>2026-09-07 15:27:33</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69215</v>
+        <v>69220</v>
       </c>
       <c r="F21" t="n">
         <v>0.066</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:02</t>
+          <t>2026-09-07 15:29:23</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:02</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:02</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37835</v>
+        <v>37836</v>
       </c>
       <c r="F25" t="n">
         <v>0.0361</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:02</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:02</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262514</v>
+        <v>262516</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:24</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F33" t="n">
         <v>0.0055</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10639</v>
+        <v>10640</v>
       </c>
       <c r="F37" t="n">
         <v>0.0101</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7201</v>
+        <v>7202</v>
       </c>
       <c r="F41" t="n">
         <v>0.0069</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79587</v>
+        <v>79588</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442953</v>
+        <v>442954</v>
       </c>
       <c r="F43" t="n">
         <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137480</v>
+        <v>137484</v>
       </c>
       <c r="F44" t="n">
         <v>0.1311</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70369</v>
+        <v>70363</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9384</v>
+        <v>9385</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0089</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33696</v>
+        <v>33697</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8511</v>
+        <v>8521</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10137</v>
+        <v>10128</v>
       </c>
       <c r="F49" t="n">
         <v>0.0097</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50951</v>
+        <v>50953</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50972</v>
+        <v>50974</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:05</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:27</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:06</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:28</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52037</v>
+        <v>52043</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51942</v>
+        <v>51930</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52900</v>
+        <v>52904</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52820</v>
+        <v>52819</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52919</v>
+        <v>52934</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52893</v>
+        <v>52887</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52343</v>
+        <v>52326</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:07</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:08</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>14607</v>
+        <v>14608</v>
       </c>
       <c r="F206" t="n">
         <v>0.0139</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27227</v>
+        <v>27249</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:08</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14919</v>
+        <v>14920</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:08</t>
+          <t>2026-09-07 15:29:29</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10418</v>
+        <v>10419</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5876</v>
+        <v>5877</v>
       </c>
       <c r="F216" t="n">
         <v>0.0056</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5816</v>
+        <v>5819</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="F224" t="n">
         <v>0.0055</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="F226" t="n">
         <v>0.0055</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="F228" t="n">
         <v>0.0055</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="F230" t="n">
         <v>0.0055</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="F232" t="n">
         <v>0.0054</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5816</v>
+        <v>5819</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F236" t="n">
         <v>0.0057</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8263,14 +8263,14 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="F238" t="n">
         <v>0.0056</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8329,14 +8329,14 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F240" t="n">
         <v>0.0055</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="F242" t="n">
         <v>0.0055</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F244" t="n">
         <v>0.0055</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8527,14 +8527,14 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F246" t="n">
         <v>0.0055</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F248" t="n">
         <v>0.0055</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8659,14 +8659,14 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="F250" t="n">
         <v>0.0055</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8791,14 +8791,14 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="F254" t="n">
         <v>0.0055</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8923,14 +8923,14 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F258" t="n">
         <v>0.0055</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5863</v>
+        <v>5864</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9055,14 +9055,14 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="F262" t="n">
         <v>0.0056</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9121,14 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="F264" t="n">
         <v>0.0056</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F266" t="n">
         <v>0.0056</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9253,14 +9253,14 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="F268" t="n">
         <v>0.0054</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5973</v>
+        <v>5974</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5982</v>
+        <v>5983</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9517,14 +9517,14 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="F276" t="n">
         <v>0.0057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9715,14 +9715,14 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="F282" t="n">
         <v>0.0057</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="F284" t="n">
         <v>0.0057</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9847,14 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="F286" t="n">
         <v>0.0056</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9913,14 +9913,14 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="F288" t="n">
         <v>0.0061</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6415</v>
+        <v>6416</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6398</v>
+        <v>6399</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6350</v>
+        <v>6351</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6340</v>
+        <v>6341</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6254</v>
+        <v>6255</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6399</v>
+        <v>6400</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -10969,14 +10969,14 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6467</v>
+        <v>6468</v>
       </c>
       <c r="F320" t="n">
         <v>0.0062</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11035,14 +11035,14 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6468</v>
+        <v>6469</v>
       </c>
       <c r="F322" t="n">
         <v>0.0062</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11101,14 +11101,14 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6483</v>
+        <v>6484</v>
       </c>
       <c r="F324" t="n">
         <v>0.0062</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11167,14 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="F326" t="n">
         <v>0.0062</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11233,14 +11233,14 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F328" t="n">
         <v>0.0062</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11299,14 +11299,14 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="F330" t="n">
         <v>0.0061</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6426</v>
+        <v>6427</v>
       </c>
       <c r="F332" t="n">
         <v>0.0061</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11431,14 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="F334" t="n">
         <v>0.006</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:15</t>
+          <t>2026-09-07 15:26:47</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14137,14 +14137,14 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6460</v>
+        <v>6461</v>
       </c>
       <c r="F416" t="n">
         <v>0.0062</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6389</v>
+        <v>6390</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6423</v>
+        <v>6424</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6435</v>
+        <v>6436</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6382</v>
+        <v>6383</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6394</v>
+        <v>6395</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4998</v>
+        <v>4999</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:04</t>
+          <t>2026-09-07 15:29:26</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15853,14 +15853,14 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5868</v>
+        <v>5870</v>
       </c>
       <c r="F468" t="n">
         <v>0.0056</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="F476" t="n">
         <v>0.0056</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5825</v>
+        <v>5828</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16546,14 +16546,14 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F489" t="n">
         <v>0.0012</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5993</v>
+        <v>5995</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16876,14 +16876,14 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F499" t="n">
         <v>0.0012</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17503,14 +17503,14 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5838</v>
+        <v>5840</v>
       </c>
       <c r="F518" t="n">
         <v>0.0056</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F520" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-06 13:30:03</t>
+          <t>2026-09-07 15:29:25</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17082</v>
+        <v>17083</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:30</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56063</v>
+        <v>56064</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:30</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17668,14 +17668,14 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>31000</v>
+        <v>31004</v>
       </c>
       <c r="F523" t="n">
         <v>0.0296</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:30</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19025</v>
+        <v>19027</v>
       </c>
       <c r="F524" t="n">
         <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:30</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133375</v>
+        <v>133376</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:30</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427187</v>
+        <v>427188</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23549</v>
+        <v>23553</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60815</v>
+        <v>60811</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7129</v>
+        <v>7131</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="F534" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5556</v>
+        <v>5558</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-06 13:27:31</t>
+          <t>2026-09-07 15:27:04</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:32</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:32</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:32</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:32</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:32</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55887</v>
+        <v>55884</v>
       </c>
       <c r="F9" t="n">
         <v>0.0533</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:33</t>
+          <t>2026-09-07 15:36:05</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69220</v>
+        <v>69216</v>
       </c>
       <c r="F21" t="n">
         <v>0.066</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:23</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262516</v>
+        <v>262515</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:24</t>
+          <t>2026-09-07 15:39:33</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79588</v>
+        <v>79587</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442954</v>
+        <v>442953</v>
       </c>
       <c r="F43" t="n">
         <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70363</v>
+        <v>70364</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9385</v>
+        <v>9384</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33697</v>
+        <v>33696</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:27</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:28</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:36</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52181</v>
+        <v>52178</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52819</v>
+        <v>52826</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85034</v>
+        <v>85033</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27249</v>
+        <v>27233</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:29</t>
+          <t>2026-09-07 15:39:37</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-07 15:26:47</t>
+          <t>2026-09-07 15:35:37</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:26</t>
+          <t>2026-09-07 15:39:35</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16678,14 +16678,14 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F493" t="n">
         <v>0.0012</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5972</v>
+        <v>5974</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-07 15:29:25</t>
+          <t>2026-09-07 15:39:34</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17083</v>
+        <v>17082</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:55</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56064</v>
+        <v>56063</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:55</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:55</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19027</v>
+        <v>19028</v>
       </c>
       <c r="F524" t="n">
         <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:55</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133376</v>
+        <v>133375</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:55</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427188</v>
+        <v>427187</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60811</v>
+        <v>60817</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7131</v>
+        <v>7130</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5558</v>
+        <v>5556</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27:04</t>
+          <t>2026-09-07 15:35:56</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19445</v>
+        <v>19446</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55884</v>
+        <v>55885</v>
       </c>
       <c r="F9" t="n">
         <v>0.0533</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7023</v>
+        <v>7024</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-07 15:36:05</t>
+          <t>2026-09-08 14:04:17</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:33</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79587</v>
+        <v>79592</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442953</v>
+        <v>442958</v>
       </c>
       <c r="F43" t="n">
         <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137484</v>
+        <v>137489</v>
       </c>
       <c r="F44" t="n">
         <v>0.1311</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70364</v>
+        <v>70391</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9384</v>
+        <v>9389</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0089</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33696</v>
+        <v>33701</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8521</v>
+        <v>8513</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10128</v>
+        <v>10133</v>
       </c>
       <c r="F49" t="n">
         <v>0.0097</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:44</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:45</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53225</v>
+        <v>53208</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:36</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54483</v>
+        <v>54528</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52178</v>
+        <v>52185</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53002</v>
+        <v>53050</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0505</v>
+        <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53072</v>
+        <v>53075</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51930</v>
+        <v>51941</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54576</v>
+        <v>54572</v>
       </c>
       <c r="F182" t="n">
         <v>0.052</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53739</v>
+        <v>53737</v>
       </c>
       <c r="F183" t="n">
         <v>0.0512</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53205</v>
+        <v>53211</v>
       </c>
       <c r="F184" t="n">
         <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53075</v>
+        <v>53067</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52914</v>
+        <v>52916</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52904</v>
+        <v>52898</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52811</v>
+        <v>52814</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52826</v>
+        <v>52828</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52879</v>
+        <v>52885</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52653</v>
+        <v>52641</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52934</v>
+        <v>52923</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52898</v>
+        <v>52886</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52835</v>
+        <v>52842</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53058</v>
+        <v>53051</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53043</v>
+        <v>53042</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52887</v>
+        <v>52891</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52833</v>
+        <v>52839</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53118</v>
+        <v>53123</v>
       </c>
       <c r="F200" t="n">
         <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52326</v>
+        <v>52327</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53991</v>
+        <v>53997</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>14608</v>
+        <v>14609</v>
       </c>
       <c r="F206" t="n">
         <v>0.0139</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85033</v>
+        <v>85034</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27233</v>
+        <v>27211</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:37</t>
+          <t>2026-09-08 14:07:46</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:37</t>
+          <t>2026-09-08 14:03:17</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:35</t>
+          <t>2026-09-08 14:07:43</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -15886,14 +15886,14 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F469" t="n">
         <v>0.0014</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6067</v>
+        <v>6065</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5895</v>
+        <v>5899</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5924</v>
+        <v>5929</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5828</v>
+        <v>5827</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5930</v>
+        <v>5933</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5998</v>
+        <v>5996</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16612,14 +16612,14 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="F491" t="n">
         <v>0.0012</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16678,14 +16678,14 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F493" t="n">
         <v>0.0012</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5974</v>
+        <v>5972</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16876,14 +16876,14 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F499" t="n">
         <v>0.0012</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17140,14 +17140,14 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F507" t="n">
         <v>0.0012</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17338,14 +17338,14 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F513" t="n">
         <v>0.0012</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5916</v>
+        <v>5919</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:41</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="F520" t="n">
         <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-07 15:39:34</t>
+          <t>2026-09-08 14:07:42</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17082</v>
+        <v>17087</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:55</t>
+          <t>2026-09-08 14:03:35</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56063</v>
+        <v>56068</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:55</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17668,14 +17668,14 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>31004</v>
+        <v>31009</v>
       </c>
       <c r="F523" t="n">
         <v>0.0296</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:55</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19028</v>
+        <v>19048</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:55</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133375</v>
+        <v>133380</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:55</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427187</v>
+        <v>427192</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23553</v>
+        <v>23598</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60817</v>
+        <v>60843</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7130</v>
+        <v>7129</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="F534" t="n">
-        <v>0.0031</v>
+        <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4563</v>
+        <v>4568</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5556</v>
+        <v>5560</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-07 15:35:56</t>
+          <t>2026-09-08 14:03:36</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17244</v>
+        <v>17258</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0164</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:20</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81079</v>
+        <v>81085</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:20</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38363</v>
+        <v>38376</v>
       </c>
       <c r="F4" t="n">
         <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:20</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19446</v>
+        <v>19455</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:20</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173429</v>
+        <v>173587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1654</v>
+        <v>0.1655</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:20</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>469035</v>
+        <v>469469</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4473</v>
+        <v>0.4477</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15236</v>
+        <v>15247</v>
       </c>
       <c r="F8" t="n">
         <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55885</v>
+        <v>55938</v>
       </c>
       <c r="F9" t="n">
         <v>0.0533</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7024</v>
+        <v>7023</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8651</v>
+        <v>8649</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6386</v>
+        <v>6381</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-08 14:04:17</t>
+          <t>2026-09-09 14:06:21</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79592</v>
+        <v>79613</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442958</v>
+        <v>442971</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4224</v>
+        <v>0.4225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137489</v>
+        <v>137502</v>
       </c>
       <c r="F44" t="n">
         <v>0.1311</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9389</v>
+        <v>9394</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33701</v>
+        <v>33706</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8513</v>
+        <v>8509</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10133</v>
+        <v>10144</v>
       </c>
       <c r="F49" t="n">
         <v>0.0097</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:28</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51969</v>
+        <v>51965</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51963</v>
+        <v>51955</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0496</v>
+        <v>0.0495</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50953</v>
+        <v>50951</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50974</v>
+        <v>50972</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>51357</v>
+        <v>52177</v>
       </c>
       <c r="F72" t="n">
-        <v>0.049</v>
+        <v>0.0498</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52958</v>
+        <v>52948</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52909</v>
+        <v>52911</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3115,14 +3115,14 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>51192</v>
+        <v>52045</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0488</v>
+        <v>0.0496</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:44</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:31</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:45</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53208</v>
+        <v>53229</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52043</v>
+        <v>52037</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54528</v>
+        <v>54518</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52185</v>
+        <v>52179</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53050</v>
+        <v>53030</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53075</v>
+        <v>53080</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:32</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51941</v>
+        <v>51946</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54572</v>
+        <v>54583</v>
       </c>
       <c r="F182" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53211</v>
+        <v>53197</v>
       </c>
       <c r="F184" t="n">
         <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53067</v>
+        <v>53062</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52916</v>
+        <v>52911</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52898</v>
+        <v>52901</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52814</v>
+        <v>52819</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52828</v>
+        <v>52824</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52885</v>
+        <v>52883</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52641</v>
+        <v>52650</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52923</v>
+        <v>52918</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52886</v>
+        <v>52889</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52842</v>
+        <v>52836</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53051</v>
+        <v>53061</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53042</v>
+        <v>53066</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52992</v>
+        <v>52994</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52839</v>
+        <v>52845</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53123</v>
+        <v>53125</v>
       </c>
       <c r="F200" t="n">
         <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52327</v>
+        <v>52321</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53997</v>
+        <v>53983</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>14609</v>
+        <v>14608</v>
       </c>
       <c r="F206" t="n">
         <v>0.0139</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85034</v>
+        <v>85033</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27211</v>
+        <v>27207</v>
       </c>
       <c r="F208" t="n">
-        <v>0.026</v>
+        <v>0.0259</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14920</v>
+        <v>14919</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:46</t>
+          <t>2026-09-09 14:07:33</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10419</v>
+        <v>10420</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5877</v>
+        <v>5876</v>
       </c>
       <c r="F216" t="n">
         <v>0.0056</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5885</v>
+        <v>5884</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5817</v>
+        <v>5816</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8956,14 +8956,14 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1194</v>
+        <v>1214</v>
       </c>
       <c r="F259" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5864</v>
+        <v>5879</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5817</v>
+        <v>5816</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5974</v>
+        <v>5973</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9418,14 +9418,14 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F273" t="n">
         <v>0.0012</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5983</v>
+        <v>5982</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9616,14 +9616,14 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="F279" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5942</v>
+        <v>5961</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:17</t>
+          <t>2026-09-09 14:05:50</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:43</t>
+          <t>2026-09-09 14:07:30</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15853,14 +15853,14 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5870</v>
+        <v>5869</v>
       </c>
       <c r="F468" t="n">
         <v>0.0056</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5889</v>
+        <v>5887</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5899</v>
+        <v>5898</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5929</v>
+        <v>5923</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6080</v>
+        <v>6077</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16348,14 +16348,14 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F483" t="n">
         <v>0.0012</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5959</v>
+        <v>5958</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5933</v>
+        <v>5931</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5996</v>
+        <v>5999</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5995</v>
+        <v>5994</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16942,14 +16942,14 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F501" t="n">
         <v>0.0012</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6018</v>
+        <v>6016</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17140,14 +17140,14 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="F507" t="n">
         <v>0.0012</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17206,14 +17206,14 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F509" t="n">
         <v>0.0012</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5919</v>
+        <v>5921</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:41</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6033</v>
+        <v>6028</v>
       </c>
       <c r="F520" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-08 14:07:42</t>
+          <t>2026-09-09 14:07:29</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17087</v>
+        <v>17094</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:35</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56068</v>
+        <v>56075</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19048</v>
+        <v>19036</v>
       </c>
       <c r="F524" t="n">
         <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133380</v>
+        <v>133387</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427192</v>
+        <v>427199</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23598</v>
+        <v>23600</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60843</v>
+        <v>60837</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3307</v>
+        <v>3309</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4568</v>
+        <v>4561</v>
       </c>
       <c r="F535" t="n">
-        <v>0.0044</v>
+        <v>0.0043</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5560</v>
+        <v>5564</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-08 14:03:36</t>
+          <t>2026-09-09 14:06:06</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17258</v>
+        <v>17260</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:20</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81085</v>
+        <v>81087</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:20</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:20</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:20</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173587</v>
+        <v>173588</v>
       </c>
       <c r="F6" t="n">
         <v>0.1655</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:20</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>469469</v>
+        <v>469470</v>
       </c>
       <c r="F7" t="n">
         <v>0.4477</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15247</v>
+        <v>15248</v>
       </c>
       <c r="F8" t="n">
         <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55938</v>
+        <v>55934</v>
       </c>
       <c r="F9" t="n">
         <v>0.0533</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7023</v>
+        <v>7022</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8649</v>
+        <v>8651</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6381</v>
+        <v>6383</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:21</t>
+          <t>2026-09-10 14:01:20</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:02</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69216</v>
+        <v>69215</v>
       </c>
       <c r="F21" t="n">
         <v>0.066</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:01</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:01</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:01</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37836</v>
+        <v>37835</v>
       </c>
       <c r="F25" t="n">
         <v>0.0361</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:01</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:01</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:02</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:02</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262515</v>
+        <v>262518</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:02</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79613</v>
+        <v>79612</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442971</v>
+        <v>442970</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4225</v>
+        <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70391</v>
+        <v>70389</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33706</v>
+        <v>33705</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8509</v>
+        <v>8510</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10144</v>
+        <v>10135</v>
       </c>
       <c r="F49" t="n">
         <v>0.0097</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:28</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51965</v>
+        <v>51974</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51955</v>
+        <v>51968</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0495</v>
+        <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50951</v>
+        <v>50952</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50972</v>
+        <v>50973</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52948</v>
+        <v>52957</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52911</v>
+        <v>52915</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:05</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:31</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:06</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53229</v>
+        <v>53228</v>
       </c>
       <c r="F175" t="n">
         <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52037</v>
+        <v>52059</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54518</v>
+        <v>54512</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52179</v>
+        <v>52181</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53030</v>
+        <v>53038</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53080</v>
+        <v>53079</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:32</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51946</v>
+        <v>51942</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54583</v>
+        <v>54597</v>
       </c>
       <c r="F182" t="n">
         <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53737</v>
+        <v>53742</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0512</v>
+        <v>0.0513</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53197</v>
+        <v>53220</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53062</v>
+        <v>53083</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52911</v>
+        <v>52916</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52901</v>
+        <v>52904</v>
       </c>
       <c r="F187" t="n">
         <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52819</v>
+        <v>52818</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52824</v>
+        <v>52822</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52883</v>
+        <v>52885</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52650</v>
+        <v>52648</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52918</v>
+        <v>52927</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52889</v>
+        <v>52884</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52836</v>
+        <v>52853</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53061</v>
+        <v>53085</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53066</v>
+        <v>53079</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52891</v>
+        <v>52893</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52845</v>
+        <v>52865</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53125</v>
+        <v>53106</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0507</v>
+        <v>0.0506</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52321</v>
+        <v>52337</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53983</v>
+        <v>54007</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85033</v>
+        <v>85036</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27207</v>
+        <v>27241</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0259</v>
+        <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:33</t>
+          <t>2026-09-10 14:05:07</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5816</v>
+        <v>5818</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5816</v>
+        <v>5818</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5973</v>
+        <v>5972</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9418,14 +9418,14 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F273" t="n">
         <v>0.0012</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05:50</t>
+          <t>2026-09-10 14:00:31</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:30</t>
+          <t>2026-09-10 14:05:04</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5939</v>
+        <v>5937</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15886,14 +15886,14 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F469" t="n">
         <v>0.0014</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6068</v>
+        <v>6066</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5898</v>
+        <v>5900</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5923</v>
+        <v>5926</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6077</v>
+        <v>6080</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5999</v>
+        <v>5998</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5973</v>
+        <v>5972</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17008,14 +17008,14 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F503" t="n">
         <v>0.0012</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6018</v>
+        <v>6016</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6024</v>
+        <v>6026</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6012</v>
+        <v>6014</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17338,14 +17338,14 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F513" t="n">
         <v>0.0012</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5921</v>
+        <v>5918</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17470,14 +17470,14 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F517" t="n">
         <v>0.0011</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6028</v>
+        <v>6030</v>
       </c>
       <c r="F520" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-09 14:07:29</t>
+          <t>2026-09-10 14:05:03</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17094</v>
+        <v>17091</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56075</v>
+        <v>56072</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19036</v>
+        <v>19035</v>
       </c>
       <c r="F524" t="n">
         <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133387</v>
+        <v>133384</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427199</v>
+        <v>427196</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23600</v>
+        <v>23572</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60837</v>
+        <v>60830</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3309</v>
+        <v>3306</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4561</v>
+        <v>4562</v>
       </c>
       <c r="F535" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5564</v>
+        <v>5559</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-09 14:06:06</t>
+          <t>2026-09-10 14:00:50</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17260</v>
+        <v>17284</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81087</v>
+        <v>81095</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38376</v>
+        <v>38409</v>
       </c>
       <c r="F4" t="n">
         <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19455</v>
+        <v>19466</v>
       </c>
       <c r="F5" t="n">
         <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173588</v>
+        <v>173890</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1655</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>469470</v>
+        <v>470324</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4477</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15248</v>
+        <v>15243</v>
       </c>
       <c r="F8" t="n">
         <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>55934</v>
+        <v>56027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0533</v>
+        <v>0.0534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8651</v>
+        <v>8650</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5306</v>
+        <v>5297</v>
       </c>
       <c r="F16" t="n">
         <v>0.0051</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6383</v>
+        <v>6367</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-10 14:01:20</t>
+          <t>2026-09-11 14:00:02</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:02</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:01</t>
+          <t>2026-09-11 14:04:04</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:01</t>
+          <t>2026-09-11 14:04:04</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:01</t>
+          <t>2026-09-11 14:04:04</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:01</t>
+          <t>2026-09-11 14:04:04</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:01</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:02</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:02</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262518</v>
+        <v>262514</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:02</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5783</v>
+        <v>5782</v>
       </c>
       <c r="F33" t="n">
         <v>0.0055</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10640</v>
+        <v>10639</v>
       </c>
       <c r="F37" t="n">
         <v>0.0101</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7202</v>
+        <v>7201</v>
       </c>
       <c r="F41" t="n">
         <v>0.0069</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:05</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79612</v>
+        <v>79630</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442970</v>
+        <v>442972</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4224</v>
+        <v>0.4225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137502</v>
+        <v>137534</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1311</v>
+        <v>0.1312</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70389</v>
+        <v>70399</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9393</v>
+        <v>9386</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33705</v>
+        <v>33698</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8510</v>
+        <v>8493</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10135</v>
+        <v>10105</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51974</v>
+        <v>51957</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51968</v>
+        <v>51963</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52178</v>
+        <v>52162</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0498</v>
+        <v>0.0497</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50952</v>
+        <v>50955</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50973</v>
+        <v>50976</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>49719</v>
+        <v>50542</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0474</v>
+        <v>0.0482</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2653,14 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>42030</v>
+        <v>42871</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0401</v>
+        <v>0.0409</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>49843</v>
+        <v>50674</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0475</v>
+        <v>0.0483</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2719,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>42034</v>
+        <v>42855</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0401</v>
+        <v>0.0409</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52199</v>
+        <v>52183</v>
       </c>
       <c r="F77" t="n">
         <v>0.0498</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52957</v>
+        <v>52950</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52915</v>
+        <v>52911</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:05</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:08</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:06</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53228</v>
+        <v>53229</v>
       </c>
       <c r="F175" t="n">
         <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52059</v>
+        <v>52041</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54512</v>
+        <v>54526</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52181</v>
+        <v>52179</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53038</v>
+        <v>53042</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53079</v>
+        <v>53078</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51942</v>
+        <v>51934</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54597</v>
+        <v>54572</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0521</v>
+        <v>0.052</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53742</v>
+        <v>53735</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53220</v>
+        <v>53219</v>
       </c>
       <c r="F184" t="n">
         <v>0.0508</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53083</v>
+        <v>53066</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52916</v>
+        <v>52909</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52904</v>
+        <v>52898</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52818</v>
+        <v>52814</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52822</v>
+        <v>52820</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52885</v>
+        <v>52879</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52648</v>
+        <v>52643</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52927</v>
+        <v>52915</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52884</v>
+        <v>52882</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52853</v>
+        <v>52842</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53085</v>
+        <v>53089</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52994</v>
+        <v>52999</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52865</v>
+        <v>52845</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53106</v>
+        <v>53120</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0506</v>
+        <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52337</v>
+        <v>52335</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>54007</v>
+        <v>53997</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85036</v>
+        <v>85035</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27241</v>
+        <v>27225</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14919</v>
+        <v>14912</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:07</t>
+          <t>2026-09-11 14:04:09</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10420</v>
+        <v>10423</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F219" t="n">
         <v>0.0012</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5818</v>
+        <v>5816</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8626,14 +8626,14 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>959</v>
+        <v>976</v>
       </c>
       <c r="F249" t="n">
         <v>0.0009</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8659,14 +8659,14 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5777</v>
+        <v>5792</v>
       </c>
       <c r="F250" t="n">
         <v>0.0055</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8692,14 +8692,14 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="F251" t="n">
         <v>0.0009</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5757</v>
+        <v>5775</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8758,14 +8758,14 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>963</v>
+        <v>980</v>
       </c>
       <c r="F253" t="n">
         <v>0.0009</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8791,14 +8791,14 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5767</v>
+        <v>5783</v>
       </c>
       <c r="F254" t="n">
         <v>0.0055</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8824,14 +8824,14 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="F255" t="n">
         <v>0.0009</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5748</v>
+        <v>5766</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9286,14 +9286,14 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F269" t="n">
         <v>0.0012</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5818</v>
+        <v>5816</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5982</v>
+        <v>5981</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -9913,14 +9913,14 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6404</v>
+        <v>6403</v>
       </c>
       <c r="F288" t="n">
         <v>0.0061</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6416</v>
+        <v>6415</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6189</v>
+        <v>6188</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6141</v>
+        <v>6140</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6399</v>
+        <v>6398</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6351</v>
+        <v>6350</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5309</v>
+        <v>5308</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5277</v>
+        <v>5276</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6401</v>
+        <v>6400</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6341</v>
+        <v>6340</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6299</v>
+        <v>6298</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6255</v>
+        <v>6254</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6387</v>
+        <v>6386</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6400</v>
+        <v>6399</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6049</v>
+        <v>6048</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5992</v>
+        <v>5991</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11101,14 +11101,14 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6484</v>
+        <v>6483</v>
       </c>
       <c r="F324" t="n">
         <v>0.0062</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11167,14 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6456</v>
+        <v>6455</v>
       </c>
       <c r="F326" t="n">
         <v>0.0062</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11299,14 +11299,14 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6405</v>
+        <v>6404</v>
       </c>
       <c r="F330" t="n">
         <v>0.0061</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="F332" t="n">
         <v>0.0061</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11431,14 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6305</v>
+        <v>6304</v>
       </c>
       <c r="F334" t="n">
         <v>0.006</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:31</t>
+          <t>2026-09-11 13:59:20</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6386</v>
+        <v>6385</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6408</v>
+        <v>6407</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5682</v>
+        <v>5681</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5646</v>
+        <v>5645</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6390</v>
+        <v>6389</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6418</v>
+        <v>6417</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6329</v>
+        <v>6328</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6324</v>
+        <v>6323</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6424</v>
+        <v>6423</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6470</v>
+        <v>6469</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6436</v>
+        <v>6435</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6437</v>
+        <v>6436</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6391</v>
+        <v>6390</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6407</v>
+        <v>6406</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6383</v>
+        <v>6382</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6395</v>
+        <v>6394</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4999</v>
+        <v>4998</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6446</v>
+        <v>6445</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6470</v>
+        <v>6469</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6220</v>
+        <v>6219</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:04</t>
+          <t>2026-09-11 14:04:07</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5937</v>
+        <v>5939</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15820,14 +15820,14 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F467" t="n">
         <v>0.0011</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15886,14 +15886,14 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="F469" t="n">
         <v>0.0014</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="F476" t="n">
         <v>0.0057</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5828</v>
+        <v>5827</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6080</v>
+        <v>6081</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5932</v>
+        <v>5930</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6006</v>
+        <v>6008</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16942,14 +16942,14 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F501" t="n">
         <v>0.0012</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17008,14 +17008,14 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F503" t="n">
         <v>0.0012</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6016</v>
+        <v>6018</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6026</v>
+        <v>6024</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6014</v>
+        <v>6011</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17503,14 +17503,14 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5840</v>
+        <v>5839</v>
       </c>
       <c r="F518" t="n">
         <v>0.0056</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17536,14 +17536,14 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F519" t="n">
         <v>0.0013</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-10 14:05:03</t>
+          <t>2026-09-11 14:04:06</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17091</v>
+        <v>17085</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56072</v>
+        <v>56066</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19035</v>
+        <v>19038</v>
       </c>
       <c r="F524" t="n">
         <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133384</v>
+        <v>133378</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427196</v>
+        <v>427190</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23572</v>
+        <v>23559</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60830</v>
+        <v>60839</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4562</v>
+        <v>4568</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5559</v>
+        <v>5558</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:50</t>
+          <t>2026-09-11 13:59:39</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17284</v>
+        <v>15517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81095</v>
+        <v>72996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0696</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38409</v>
+        <v>34386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19466</v>
+        <v>17841</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0186</v>
+        <v>0.017</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173890</v>
+        <v>152504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.1454</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470324</v>
+        <v>416646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.3973</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15243</v>
+        <v>14481</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0145</v>
+        <v>0.0138</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56027</v>
+        <v>50464</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0534</v>
+        <v>0.0481</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7022</v>
+        <v>7023</v>
       </c>
       <c r="F13" t="n">
         <v>0.0067</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2136</v>
+        <v>1920</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0018</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8650</v>
+        <v>7702</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0073</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5297</v>
+        <v>5179</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.0049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6367</v>
+        <v>6236</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.0059</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:02</t>
+          <t>2026-09-11 14:08:13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:04</t>
+          <t>2026-09-11 14:10:05</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:04</t>
+          <t>2026-09-11 14:10:05</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:04</t>
+          <t>2026-09-11 14:10:05</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:04</t>
+          <t>2026-09-11 14:10:05</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:05</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:05</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79630</v>
+        <v>77756</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0759</v>
+        <v>0.0742</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442972</v>
+        <v>429806</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4225</v>
+        <v>0.4099</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137534</v>
+        <v>133244</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1312</v>
+        <v>0.1271</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70399</v>
+        <v>68123</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9386</v>
+        <v>9104</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33698</v>
+        <v>32552</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0321</v>
+        <v>0.031</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8493</v>
+        <v>8384</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0081</v>
+        <v>0.008</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10105</v>
+        <v>9955</v>
       </c>
       <c r="F49" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:09</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:08</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53229</v>
+        <v>53215</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52179</v>
+        <v>52185</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53042</v>
+        <v>53038</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53078</v>
+        <v>53080</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51934</v>
+        <v>51956</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54572</v>
+        <v>54577</v>
       </c>
       <c r="F182" t="n">
         <v>0.052</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53735</v>
+        <v>53740</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0512</v>
+        <v>0.0513</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53219</v>
+        <v>53198</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53066</v>
+        <v>53079</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52909</v>
+        <v>52915</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52898</v>
+        <v>52896</v>
       </c>
       <c r="F187" t="n">
         <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52814</v>
+        <v>52816</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52820</v>
+        <v>52830</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52879</v>
+        <v>52885</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52643</v>
+        <v>52649</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52915</v>
+        <v>52918</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52882</v>
+        <v>52889</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52842</v>
+        <v>52851</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53089</v>
+        <v>53092</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53079</v>
+        <v>53078</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52999</v>
+        <v>52994</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52893</v>
+        <v>52891</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52845</v>
+        <v>52843</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:10</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53120</v>
+        <v>53108</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0507</v>
+        <v>0.0506</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:11</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:11</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53997</v>
+        <v>53994</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:11</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>14608</v>
+        <v>14607</v>
       </c>
       <c r="F206" t="n">
         <v>0.0139</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85035</v>
+        <v>85034</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27225</v>
+        <v>27273</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:11</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:09</t>
+          <t>2026-09-11 14:10:11</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20560</v>
+        <v>19908</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0196</v>
+        <v>0.019</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10423</v>
+        <v>10276</v>
       </c>
       <c r="F212" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:08</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5876</v>
+        <v>5875</v>
       </c>
       <c r="F216" t="n">
         <v>0.0056</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5885</v>
+        <v>5884</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5816</v>
+        <v>5815</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5729</v>
+        <v>5728</v>
       </c>
       <c r="F224" t="n">
         <v>0.0055</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5730</v>
+        <v>5729</v>
       </c>
       <c r="F228" t="n">
         <v>0.0055</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5767</v>
+        <v>5766</v>
       </c>
       <c r="F230" t="n">
         <v>0.0055</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5665</v>
+        <v>5664</v>
       </c>
       <c r="F232" t="n">
         <v>0.0054</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8263,14 +8263,14 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5902</v>
+        <v>5901</v>
       </c>
       <c r="F238" t="n">
         <v>0.0056</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8329,14 +8329,14 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5805</v>
+        <v>5804</v>
       </c>
       <c r="F240" t="n">
         <v>0.0055</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5807</v>
+        <v>5806</v>
       </c>
       <c r="F242" t="n">
         <v>0.0055</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F244" t="n">
         <v>0.0055</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5747</v>
+        <v>5746</v>
       </c>
       <c r="F248" t="n">
         <v>0.0055</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8659,14 +8659,14 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5792</v>
+        <v>5791</v>
       </c>
       <c r="F250" t="n">
         <v>0.0055</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8791,14 +8791,14 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5783</v>
+        <v>5782</v>
       </c>
       <c r="F254" t="n">
         <v>0.0055</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5766</v>
+        <v>5765</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8923,14 +8923,14 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5794</v>
+        <v>5793</v>
       </c>
       <c r="F258" t="n">
         <v>0.0055</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9055,14 +9055,14 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5909</v>
+        <v>5908</v>
       </c>
       <c r="F262" t="n">
         <v>0.0056</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9121,14 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="F264" t="n">
         <v>0.0056</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="F266" t="n">
         <v>0.0056</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9253,14 +9253,14 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5685</v>
+        <v>5684</v>
       </c>
       <c r="F268" t="n">
         <v>0.0054</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5816</v>
+        <v>5815</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5972</v>
+        <v>5971</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5981</v>
+        <v>5980</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9715,14 +9715,14 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="F282" t="n">
         <v>0.0057</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="F284" t="n">
         <v>0.0057</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9847,14 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="F286" t="n">
         <v>0.0056</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -10969,14 +10969,14 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6468</v>
+        <v>6467</v>
       </c>
       <c r="F320" t="n">
         <v>0.0062</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11035,14 +11035,14 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6469</v>
+        <v>6468</v>
       </c>
       <c r="F322" t="n">
         <v>0.0062</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11233,14 +11233,14 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F328" t="n">
         <v>0.0062</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:20</t>
+          <t>2026-09-11 14:07:25</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14137,14 +14137,14 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6461</v>
+        <v>6460</v>
       </c>
       <c r="F416" t="n">
         <v>0.0062</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:07</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5939</v>
+        <v>5935</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15820,14 +15820,14 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F467" t="n">
         <v>0.0011</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15853,14 +15853,14 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5869</v>
+        <v>5868</v>
       </c>
       <c r="F468" t="n">
         <v>0.0056</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5888</v>
+        <v>5886</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5899</v>
+        <v>5898</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5927</v>
+        <v>5925</v>
       </c>
       <c r="F476" t="n">
         <v>0.0057</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6081</v>
+        <v>6075</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5922</v>
+        <v>5920</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16348,14 +16348,14 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="F483" t="n">
         <v>0.0012</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5997</v>
+        <v>5996</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5972</v>
+        <v>5971</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5994</v>
+        <v>5992</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16942,14 +16942,14 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="F501" t="n">
         <v>0.0012</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17008,14 +17008,14 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F503" t="n">
         <v>0.0012</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6018</v>
+        <v>6016</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17338,14 +17338,14 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F513" t="n">
         <v>0.0012</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:07</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5918</v>
+        <v>5917</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17470,14 +17470,14 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F517" t="n">
         <v>0.0011</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17536,14 +17536,14 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F519" t="n">
         <v>0.0013</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="F520" t="n">
-        <v>0.0058</v>
+        <v>0.0057</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-11 14:04:06</t>
+          <t>2026-09-11 14:10:06</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17085</v>
+        <v>17090</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56066</v>
+        <v>56071</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19038</v>
+        <v>19040</v>
       </c>
       <c r="F524" t="n">
         <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133378</v>
+        <v>133383</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427190</v>
+        <v>427195</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23559</v>
+        <v>23598</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7129</v>
+        <v>7130</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4568</v>
+        <v>4565</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5558</v>
+        <v>5562</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-11 13:59:39</t>
+          <t>2026-09-11 14:07:40</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15517</v>
+        <v>17284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0148</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72996</v>
+        <v>81095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0696</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34386</v>
+        <v>38409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0328</v>
+        <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17841</v>
+        <v>19469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.017</v>
+        <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>152504</v>
+        <v>173890</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1454</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>416646</v>
+        <v>470324</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3973</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14481</v>
+        <v>15243</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0138</v>
+        <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50464</v>
+        <v>56025</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0481</v>
+        <v>0.0534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1920</v>
+        <v>2136</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0018</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:05</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7702</v>
+        <v>8650</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0073</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5179</v>
+        <v>5297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0049</v>
+        <v>0.0051</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6236</v>
+        <v>6371</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0059</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-11 14:08:13</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:05</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:05</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:05</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:05</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:05</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>77756</v>
+        <v>79637</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0742</v>
+        <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>429806</v>
+        <v>442979</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4099</v>
+        <v>0.4225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>133244</v>
+        <v>137534</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1271</v>
+        <v>0.1312</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>68123</v>
+        <v>70394</v>
       </c>
       <c r="F45" t="n">
-        <v>0.065</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9104</v>
+        <v>9393</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>32552</v>
+        <v>33705</v>
       </c>
       <c r="F47" t="n">
-        <v>0.031</v>
+        <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8384</v>
+        <v>8517</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008</v>
+        <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9955</v>
+        <v>10112</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51957</v>
+        <v>51968</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51963</v>
+        <v>51962</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52950</v>
+        <v>52951</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52911</v>
+        <v>52915</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:08</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:09</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:09</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53215</v>
+        <v>53225</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52041</v>
+        <v>52039</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52185</v>
+        <v>52183</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53038</v>
+        <v>52972</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0506</v>
+        <v>0.0505</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53080</v>
+        <v>53088</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51956</v>
+        <v>51951</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54577</v>
+        <v>54583</v>
       </c>
       <c r="F182" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53740</v>
+        <v>53754</v>
       </c>
       <c r="F183" t="n">
         <v>0.0513</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53198</v>
+        <v>53216</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53079</v>
+        <v>53081</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52896</v>
+        <v>52902</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52816</v>
+        <v>52814</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52830</v>
+        <v>52821</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52885</v>
+        <v>52881</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52649</v>
+        <v>52642</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52918</v>
+        <v>52934</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52889</v>
+        <v>52886</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52851</v>
+        <v>52843</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53092</v>
+        <v>53088</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53078</v>
+        <v>53070</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52994</v>
+        <v>52993</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52891</v>
+        <v>52886</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52843</v>
+        <v>52846</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:10</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53108</v>
+        <v>53114</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0506</v>
+        <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:11</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52335</v>
+        <v>52322</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:11</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53994</v>
+        <v>53997</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:11</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85034</v>
+        <v>85030</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27273</v>
+        <v>27236</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:11</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:11</t>
+          <t>2026-09-12 13:19:10</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>19908</v>
+        <v>20560</v>
       </c>
       <c r="F211" t="n">
-        <v>0.019</v>
+        <v>0.0196</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10276</v>
+        <v>10424</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0098</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:08</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="F224" t="n">
         <v>0.0055</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="F228" t="n">
         <v>0.0055</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="F230" t="n">
         <v>0.0055</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="F232" t="n">
         <v>0.0054</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5941</v>
+        <v>5940</v>
       </c>
       <c r="F236" t="n">
         <v>0.0057</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="F242" t="n">
         <v>0.0055</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F244" t="n">
         <v>0.0055</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F248" t="n">
         <v>0.0055</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8923,14 +8923,14 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F258" t="n">
         <v>0.0055</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9055,14 +9055,14 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="F262" t="n">
         <v>0.0056</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9121,14 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="F264" t="n">
         <v>0.0056</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F266" t="n">
         <v>0.0056</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9715,14 +9715,14 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="F282" t="n">
         <v>0.0057</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="F284" t="n">
         <v>0.0057</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9847,14 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="F286" t="n">
         <v>0.0056</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9913,14 +9913,14 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="F288" t="n">
         <v>0.0061</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6415</v>
+        <v>6416</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6398</v>
+        <v>6399</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6350</v>
+        <v>6351</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6340</v>
+        <v>6341</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6254</v>
+        <v>6255</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6399</v>
+        <v>6400</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -10969,14 +10969,14 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6467</v>
+        <v>6468</v>
       </c>
       <c r="F320" t="n">
         <v>0.0062</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11035,14 +11035,14 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6468</v>
+        <v>6469</v>
       </c>
       <c r="F322" t="n">
         <v>0.0062</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11101,14 +11101,14 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6483</v>
+        <v>6484</v>
       </c>
       <c r="F324" t="n">
         <v>0.0062</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11167,14 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="F326" t="n">
         <v>0.0062</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11233,14 +11233,14 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F328" t="n">
         <v>0.0062</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11299,14 +11299,14 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="F330" t="n">
         <v>0.0061</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6426</v>
+        <v>6427</v>
       </c>
       <c r="F332" t="n">
         <v>0.0061</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11431,14 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="F334" t="n">
         <v>0.006</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:25</t>
+          <t>2026-09-12 13:18:13</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14137,14 +14137,14 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6460</v>
+        <v>6461</v>
       </c>
       <c r="F416" t="n">
         <v>0.0062</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6389</v>
+        <v>6390</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6423</v>
+        <v>6424</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6435</v>
+        <v>6436</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6382</v>
+        <v>6383</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6394</v>
+        <v>6395</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4998</v>
+        <v>4999</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:07</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5935</v>
+        <v>5938</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6068</v>
+        <v>6065</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5898</v>
+        <v>5893</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5925</v>
+        <v>5922</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5827</v>
+        <v>5826</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6075</v>
+        <v>6077</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5920</v>
+        <v>5923</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16348,14 +16348,14 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="F483" t="n">
         <v>0.0012</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5957</v>
+        <v>5956</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5993</v>
+        <v>5992</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16678,14 +16678,14 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F493" t="n">
         <v>0.0012</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5971</v>
+        <v>5970</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17206,14 +17206,14 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F509" t="n">
         <v>0.0012</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6012</v>
+        <v>6010</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:07</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17503,14 +17503,14 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5839</v>
+        <v>5838</v>
       </c>
       <c r="F518" t="n">
         <v>0.0056</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17536,14 +17536,14 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F519" t="n">
         <v>0.0013</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="F520" t="n">
         <v>0.0057</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-11 14:10:06</t>
+          <t>2026-09-12 13:19:06</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17090</v>
+        <v>17092</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56071</v>
+        <v>56073</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19040</v>
+        <v>19031</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133383</v>
+        <v>133385</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427195</v>
+        <v>427197</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23598</v>
+        <v>23561</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60839</v>
+        <v>60828</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:31</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7130</v>
+        <v>7132</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3305</v>
+        <v>3309</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4565</v>
+        <v>4566</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5562</v>
+        <v>5559</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-11 14:07:40</t>
+          <t>2026-09-12 13:18:32</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:54</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19469</v>
+        <v>19473</v>
       </c>
       <c r="F5" t="n">
         <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:05</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6371</v>
+        <v>6368</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:24:55</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:20</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:08</t>
+          <t>2026-09-12 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:24</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:09</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85030</v>
+        <v>85035</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27236</v>
+        <v>27248</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:25</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14912</v>
+        <v>14913</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:10</t>
+          <t>2026-09-12 13:27:26</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10424</v>
+        <v>10423</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5729</v>
+        <v>5728</v>
       </c>
       <c r="F224" t="n">
         <v>0.0055</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5735</v>
+        <v>5734</v>
       </c>
       <c r="F226" t="n">
         <v>0.0055</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5730</v>
+        <v>5729</v>
       </c>
       <c r="F228" t="n">
         <v>0.0055</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5767</v>
+        <v>5766</v>
       </c>
       <c r="F230" t="n">
         <v>0.0055</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5665</v>
+        <v>5664</v>
       </c>
       <c r="F232" t="n">
         <v>0.0054</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5807</v>
+        <v>5806</v>
       </c>
       <c r="F242" t="n">
         <v>0.0055</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5765</v>
+        <v>5764</v>
       </c>
       <c r="F244" t="n">
         <v>0.0055</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8527,14 +8527,14 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5747</v>
+        <v>5746</v>
       </c>
       <c r="F246" t="n">
         <v>0.0055</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5747</v>
+        <v>5746</v>
       </c>
       <c r="F248" t="n">
         <v>0.0055</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5775</v>
+        <v>5774</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5766</v>
+        <v>5765</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8923,14 +8923,14 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5794</v>
+        <v>5793</v>
       </c>
       <c r="F258" t="n">
         <v>0.0055</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5879</v>
+        <v>5878</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9055,14 +9055,14 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5909</v>
+        <v>5908</v>
       </c>
       <c r="F262" t="n">
         <v>0.0056</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9121,14 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5891</v>
+        <v>5890</v>
       </c>
       <c r="F264" t="n">
         <v>0.0056</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="F266" t="n">
         <v>0.0056</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5972</v>
+        <v>5971</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5983</v>
+        <v>5982</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9517,14 +9517,14 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5937</v>
+        <v>5936</v>
       </c>
       <c r="F276" t="n">
         <v>0.0057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5961</v>
+        <v>5960</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9715,14 +9715,14 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5929</v>
+        <v>5928</v>
       </c>
       <c r="F282" t="n">
         <v>0.0057</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5938</v>
+        <v>5937</v>
       </c>
       <c r="F284" t="n">
         <v>0.0057</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9847,14 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5922</v>
+        <v>5921</v>
       </c>
       <c r="F286" t="n">
         <v>0.0056</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9913,14 +9913,14 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6404</v>
+        <v>6403</v>
       </c>
       <c r="F288" t="n">
         <v>0.0061</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6416</v>
+        <v>6415</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6189</v>
+        <v>6188</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6141</v>
+        <v>6140</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6399</v>
+        <v>6398</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6351</v>
+        <v>6350</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5309</v>
+        <v>5308</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5277</v>
+        <v>5276</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6401</v>
+        <v>6400</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6341</v>
+        <v>6340</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6299</v>
+        <v>6298</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6255</v>
+        <v>6254</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6387</v>
+        <v>6386</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6400</v>
+        <v>6399</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6049</v>
+        <v>6048</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5992</v>
+        <v>5991</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -10969,14 +10969,14 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6468</v>
+        <v>6467</v>
       </c>
       <c r="F320" t="n">
         <v>0.0062</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11035,14 +11035,14 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6469</v>
+        <v>6468</v>
       </c>
       <c r="F322" t="n">
         <v>0.0062</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11101,14 +11101,14 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6484</v>
+        <v>6483</v>
       </c>
       <c r="F324" t="n">
         <v>0.0062</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11167,14 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6456</v>
+        <v>6455</v>
       </c>
       <c r="F326" t="n">
         <v>0.0062</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11233,14 +11233,14 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F328" t="n">
         <v>0.0062</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11299,14 +11299,14 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6405</v>
+        <v>6404</v>
       </c>
       <c r="F330" t="n">
         <v>0.0061</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="F332" t="n">
         <v>0.0061</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11431,14 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6305</v>
+        <v>6304</v>
       </c>
       <c r="F334" t="n">
         <v>0.006</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:13</t>
+          <t>2026-09-12 13:24:13</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14137,14 +14137,14 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6461</v>
+        <v>6460</v>
       </c>
       <c r="F416" t="n">
         <v>0.0062</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6386</v>
+        <v>6385</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6408</v>
+        <v>6407</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5682</v>
+        <v>5681</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5646</v>
+        <v>5645</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6390</v>
+        <v>6389</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6418</v>
+        <v>6417</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6329</v>
+        <v>6328</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6324</v>
+        <v>6323</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6424</v>
+        <v>6423</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6470</v>
+        <v>6469</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5947</v>
+        <v>5946</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6436</v>
+        <v>6435</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6437</v>
+        <v>6436</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6391</v>
+        <v>6390</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6407</v>
+        <v>6406</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6383</v>
+        <v>6382</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6395</v>
+        <v>6394</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4999</v>
+        <v>4998</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6446</v>
+        <v>6445</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6470</v>
+        <v>6469</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6220</v>
+        <v>6219</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:07</t>
+          <t>2026-09-12 13:27:22</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-12 13:19:06</t>
+          <t>2026-09-12 13:27:21</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:28</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19031</v>
+        <v>19032</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60828</v>
+        <v>60829</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:31</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -17965,14 +17965,14 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>7132</v>
+        <v>7130</v>
       </c>
       <c r="F532" t="n">
         <v>0.0068</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-12 13:18:32</t>
+          <t>2026-09-12 13:24:29</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:54</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19473</v>
+        <v>19469</v>
       </c>
       <c r="F5" t="n">
         <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:55</t>
+          <t>2026-09-13 14:02:04</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69215</v>
+        <v>69216</v>
       </c>
       <c r="F21" t="n">
         <v>0.066</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:31</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:31</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:31</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37835</v>
+        <v>37836</v>
       </c>
       <c r="F25" t="n">
         <v>0.0361</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:31</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:31</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262514</v>
+        <v>262518</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:20</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F33" t="n">
         <v>0.0055</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10639</v>
+        <v>10640</v>
       </c>
       <c r="F37" t="n">
         <v>0.0101</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1762,14 +1762,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7201</v>
+        <v>7202</v>
       </c>
       <c r="F41" t="n">
         <v>0.0069</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:32</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79637</v>
+        <v>79636</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442979</v>
+        <v>442978</v>
       </c>
       <c r="F43" t="n">
         <v>0.4225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70394</v>
+        <v>70393</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33705</v>
+        <v>33704</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8517</v>
+        <v>8493</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10112</v>
+        <v>10115</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:23</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:35</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:24</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:36</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53225</v>
+        <v>53229</v>
       </c>
       <c r="F175" t="n">
         <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53088</v>
+        <v>53070</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51951</v>
+        <v>51952</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53754</v>
+        <v>53744</v>
       </c>
       <c r="F183" t="n">
         <v>0.0513</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52915</v>
+        <v>52913</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52642</v>
+        <v>52646</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52934</v>
+        <v>52920</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52843</v>
+        <v>52853</v>
       </c>
       <c r="F194" t="n">
         <v>0.0504</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52993</v>
+        <v>52988</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52886</v>
+        <v>52884</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53114</v>
+        <v>53118</v>
       </c>
       <c r="F200" t="n">
         <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52322</v>
+        <v>52332</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7207,14 +7207,14 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>14607</v>
+        <v>14608</v>
       </c>
       <c r="F206" t="n">
         <v>0.0139</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27248</v>
+        <v>27271</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:25</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:26</t>
+          <t>2026-09-13 14:04:37</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7537,14 +7537,14 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="F216" t="n">
         <v>0.0056</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7801,14 +7801,14 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="F224" t="n">
         <v>0.0055</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7867,14 +7867,14 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="F226" t="n">
         <v>0.0055</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7933,14 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="F228" t="n">
         <v>0.0055</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -7999,14 +7999,14 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="F230" t="n">
         <v>0.0055</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8065,14 +8065,14 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="F232" t="n">
         <v>0.0054</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="F236" t="n">
         <v>0.0057</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8263,14 +8263,14 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="F238" t="n">
         <v>0.0056</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8329,14 +8329,14 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F240" t="n">
         <v>0.0055</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8395,14 +8395,14 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="F242" t="n">
         <v>0.0055</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8461,14 +8461,14 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="F244" t="n">
         <v>0.0055</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8527,14 +8527,14 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F246" t="n">
         <v>0.0055</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F248" t="n">
         <v>0.0055</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8659,14 +8659,14 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="F250" t="n">
         <v>0.0055</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8725,14 +8725,14 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F252" t="n">
         <v>0.0055</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8791,14 +8791,14 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F254" t="n">
         <v>0.0055</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8857,14 +8857,14 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="F256" t="n">
         <v>0.0055</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8923,14 +8923,14 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F258" t="n">
         <v>0.0055</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="F260" t="n">
         <v>0.0056</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9055,14 +9055,14 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="F262" t="n">
         <v>0.0056</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9121,14 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="F264" t="n">
         <v>0.0056</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F266" t="n">
         <v>0.0056</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9253,14 +9253,14 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="F268" t="n">
         <v>0.0054</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5982</v>
+        <v>5983</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9517,14 +9517,14 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="F276" t="n">
         <v>0.0057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9649,14 +9649,14 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="F280" t="n">
         <v>0.0057</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9715,14 +9715,14 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="F282" t="n">
         <v>0.0057</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="F284" t="n">
         <v>0.0057</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9847,14 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="F286" t="n">
         <v>0.0056</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -10969,14 +10969,14 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6467</v>
+        <v>6468</v>
       </c>
       <c r="F320" t="n">
         <v>0.0062</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11035,14 +11035,14 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6468</v>
+        <v>6469</v>
       </c>
       <c r="F322" t="n">
         <v>0.0062</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11101,14 +11101,14 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6483</v>
+        <v>6484</v>
       </c>
       <c r="F324" t="n">
         <v>0.0062</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11233,14 +11233,14 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F328" t="n">
         <v>0.0062</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11299,14 +11299,14 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="F330" t="n">
         <v>0.0061</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6426</v>
+        <v>6427</v>
       </c>
       <c r="F332" t="n">
         <v>0.0061</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11431,14 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="F334" t="n">
         <v>0.006</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:13</t>
+          <t>2026-09-13 14:01:11</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -14137,14 +14137,14 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6460</v>
+        <v>6461</v>
       </c>
       <c r="F416" t="n">
         <v>0.0062</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:22</t>
+          <t>2026-09-13 14:04:34</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5938</v>
+        <v>5936</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15853,14 +15853,14 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5868</v>
+        <v>5869</v>
       </c>
       <c r="F468" t="n">
         <v>0.0056</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="F476" t="n">
         <v>0.0056</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6077</v>
+        <v>6078</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5997</v>
+        <v>5999</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17206,14 +17206,14 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F509" t="n">
         <v>0.0012</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6010</v>
+        <v>6012</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5917</v>
+        <v>5919</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17470,14 +17470,14 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F517" t="n">
         <v>0.0011</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="F520" t="n">
         <v>0.0057</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-12 13:27:21</t>
+          <t>2026-09-13 14:04:33</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17092</v>
+        <v>17091</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:28</t>
+          <t>2026-09-13 14:01:28</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56073</v>
+        <v>56072</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:28</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:28</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19032</v>
+        <v>19028</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:28</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133385</v>
+        <v>133384</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427197</v>
+        <v>427196</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23561</v>
+        <v>23575</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60829</v>
+        <v>60823</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3309</v>
+        <v>3307</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4566</v>
+        <v>4568</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5560</v>
+        <v>5562</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-12 13:24:29</t>
+          <t>2026-09-13 14:01:29</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17284</v>
+        <v>16510</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0157</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:28</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81095</v>
+        <v>77787</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:28</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38409</v>
+        <v>36507</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0348</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:28</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19469</v>
+        <v>18728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0186</v>
+        <v>0.0179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:28</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173890</v>
+        <v>164644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.157</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:28</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470324</v>
+        <v>444518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.4239</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15243</v>
+        <v>15056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0145</v>
+        <v>0.0144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56025</v>
+        <v>53292</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0534</v>
+        <v>0.0508</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2136</v>
+        <v>2038</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8650</v>
+        <v>8186</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5297</v>
+        <v>5247</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6368</v>
+        <v>6307</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-13 14:02:04</t>
+          <t>2026-09-13 14:10:29</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:31</t>
+          <t>2026-09-13 14:12:53</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:31</t>
+          <t>2026-09-13 14:12:53</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:31</t>
+          <t>2026-09-13 14:12:53</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:31</t>
+          <t>2026-09-13 14:12:53</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:31</t>
+          <t>2026-09-13 14:12:53</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262518</v>
+        <v>262515</v>
       </c>
       <c r="F29" t="n">
         <v>0.2504</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:32</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79636</v>
+        <v>78806</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0759</v>
+        <v>0.0752</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442978</v>
+        <v>437354</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4225</v>
+        <v>0.4171</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137534</v>
+        <v>135498</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1312</v>
+        <v>0.1292</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70393</v>
+        <v>69398</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9392</v>
+        <v>9258</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33704</v>
+        <v>33138</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0321</v>
+        <v>0.0316</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8493</v>
+        <v>8422</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0081</v>
+        <v>0.008</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10115</v>
+        <v>10030</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:56</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:35</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:36</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:57</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27271</v>
+        <v>27266</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:37</t>
+          <t>2026-09-13 14:12:58</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20560</v>
+        <v>20267</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0196</v>
+        <v>0.0193</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10423</v>
+        <v>10333</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9913,14 +9913,14 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="F288" t="n">
         <v>0.0061</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6415</v>
+        <v>6416</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6398</v>
+        <v>6399</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6350</v>
+        <v>6351</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6340</v>
+        <v>6341</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6254</v>
+        <v>6255</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6399</v>
+        <v>6400</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11167,14 +11167,14 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="F326" t="n">
         <v>0.0062</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:11</t>
+          <t>2026-09-13 14:09:48</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6389</v>
+        <v>6390</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6423</v>
+        <v>6424</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6435</v>
+        <v>6436</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6382</v>
+        <v>6383</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6394</v>
+        <v>6395</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4998</v>
+        <v>4999</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6469</v>
+        <v>6470</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:34</t>
+          <t>2026-09-13 14:12:55</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-13 14:04:33</t>
+          <t>2026-09-13 14:12:54</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:28</t>
+          <t>2026-09-13 14:10:04</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:28</t>
+          <t>2026-09-13 14:10:04</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:28</t>
+          <t>2026-09-13 14:10:04</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19028</v>
+        <v>19027</v>
       </c>
       <c r="F524" t="n">
         <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:28</t>
+          <t>2026-09-13 14:10:04</t>
         </is>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:04</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60823</v>
+        <v>60826</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-13 14:01:29</t>
+          <t>2026-09-13 14:10:05</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16510</v>
+        <v>17284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0157</v>
+        <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:28</t>
+          <t>2026-09-14 16:06:53</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>77787</v>
+        <v>81095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0742</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:28</t>
+          <t>2026-09-14 16:06:53</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36507</v>
+        <v>38409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0348</v>
+        <v>0.0366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:28</t>
+          <t>2026-09-14 16:06:53</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18728</v>
+        <v>19468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0179</v>
+        <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:28</t>
+          <t>2026-09-14 16:06:53</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>164644</v>
+        <v>173892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.157</v>
+        <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:28</t>
+          <t>2026-09-14 16:06:53</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>444518</v>
+        <v>470326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4239</v>
+        <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15056</v>
+        <v>15243</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0144</v>
+        <v>0.0145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53292</v>
+        <v>56030</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0508</v>
+        <v>0.0534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2038</v>
+        <v>2136</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8186</v>
+        <v>8650</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0078</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5247</v>
+        <v>5297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6307</v>
+        <v>6367</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:29</t>
+          <t>2026-09-14 16:06:54</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:53</t>
+          <t>2026-09-14 16:08:46</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:53</t>
+          <t>2026-09-14 16:08:46</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:53</t>
+          <t>2026-09-14 16:08:46</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:53</t>
+          <t>2026-09-14 16:08:46</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:53</t>
+          <t>2026-09-14 16:08:46</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>78806</v>
+        <v>79633</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0752</v>
+        <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>437354</v>
+        <v>442975</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4171</v>
+        <v>0.4225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>135498</v>
+        <v>137534</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1292</v>
+        <v>0.1312</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>69398</v>
+        <v>70402</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9258</v>
+        <v>9389</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33138</v>
+        <v>33701</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0316</v>
+        <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8422</v>
+        <v>8493</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008</v>
+        <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10030</v>
+        <v>10116</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52162</v>
+        <v>52177</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0497</v>
+        <v>0.0498</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50955</v>
+        <v>50948</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50976</v>
+        <v>50969</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52183</v>
+        <v>52198</v>
       </c>
       <c r="F77" t="n">
         <v>0.0498</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:56</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:49</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53229</v>
+        <v>53213</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:57</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52039</v>
+        <v>52065</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54526</v>
+        <v>54528</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:50</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>52972</v>
+        <v>53040</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0505</v>
+        <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53070</v>
+        <v>53078</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51952</v>
+        <v>51951</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54583</v>
+        <v>54601</v>
       </c>
       <c r="F182" t="n">
         <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53744</v>
+        <v>53746</v>
       </c>
       <c r="F183" t="n">
         <v>0.0513</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53216</v>
+        <v>53188</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53081</v>
+        <v>53082</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52913</v>
+        <v>52908</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52902</v>
+        <v>52888</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52814</v>
+        <v>52819</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52821</v>
+        <v>52825</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52881</v>
+        <v>52883</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53088</v>
+        <v>53089</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53070</v>
+        <v>53079</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52988</v>
+        <v>52995</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52884</v>
+        <v>52880</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52846</v>
+        <v>52838</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53118</v>
+        <v>53108</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0507</v>
+        <v>0.0506</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52332</v>
+        <v>52328</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85035</v>
+        <v>85033</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27266</v>
+        <v>27225</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:58</t>
+          <t>2026-09-14 16:08:51</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20267</v>
+        <v>20560</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0193</v>
+        <v>0.0196</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10333</v>
+        <v>10424</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F219" t="n">
         <v>0.0012</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F221" t="n">
         <v>0.0011</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F233" t="n">
         <v>0.0011</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5819</v>
+        <v>5818</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -9286,14 +9286,14 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F269" t="n">
         <v>0.0012</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-13 14:09:48</t>
+          <t>2026-09-14 16:06:17</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:55</t>
+          <t>2026-09-14 16:08:48</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5936</v>
+        <v>5941</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5888</v>
+        <v>5887</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5894</v>
+        <v>5898</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5923</v>
+        <v>5925</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6078</v>
+        <v>6080</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16480,14 +16480,14 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F487" t="n">
         <v>0.0012</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5999</v>
+        <v>5995</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16678,14 +16678,14 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F493" t="n">
         <v>0.0012</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16810,14 +16810,14 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F497" t="n">
         <v>0.0012</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5994</v>
+        <v>5992</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6012</v>
+        <v>6014</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17404,14 +17404,14 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="F515" t="n">
         <v>0.0012</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5919</v>
+        <v>5918</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17503,14 +17503,14 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5838</v>
+        <v>5840</v>
       </c>
       <c r="F518" t="n">
         <v>0.0056</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="F520" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-13 14:12:54</t>
+          <t>2026-09-14 16:08:47</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17091</v>
+        <v>17088</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:04</t>
+          <t>2026-09-14 16:06:36</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56072</v>
+        <v>56069</v>
       </c>
       <c r="F522" t="n">
         <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:04</t>
+          <t>2026-09-14 16:06:36</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:04</t>
+          <t>2026-09-14 16:06:36</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19027</v>
+        <v>19040</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:04</t>
+          <t>2026-09-14 16:06:36</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133384</v>
+        <v>133381</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:04</t>
+          <t>2026-09-14 16:06:36</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427196</v>
+        <v>427193</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23575</v>
+        <v>23564</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60826</v>
+        <v>60843</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5562</v>
+        <v>5568</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-13 14:10:05</t>
+          <t>2026-09-14 16:06:37</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17284</v>
+        <v>17285</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:53</t>
+          <t>2026-09-15 14:36:01</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81095</v>
+        <v>81096</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:53</t>
+          <t>2026-09-15 14:36:01</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:53</t>
+          <t>2026-09-15 14:36:01</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19468</v>
+        <v>19467</v>
       </c>
       <c r="F5" t="n">
         <v>0.0186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:53</t>
+          <t>2026-09-15 14:36:01</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173892</v>
+        <v>173891</v>
       </c>
       <c r="F6" t="n">
         <v>0.1658</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:53</t>
+          <t>2026-09-15 14:36:01</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470326</v>
+        <v>470325</v>
       </c>
       <c r="F7" t="n">
         <v>0.4485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56030</v>
+        <v>56032</v>
       </c>
       <c r="F9" t="n">
         <v>0.0534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8650</v>
+        <v>8651</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6367</v>
+        <v>6370</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:54</t>
+          <t>2026-09-15 14:36:02</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:46</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:46</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:46</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:46</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:46</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79633</v>
+        <v>79611</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442975</v>
+        <v>442953</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4225</v>
+        <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137534</v>
+        <v>137528</v>
       </c>
       <c r="F44" t="n">
         <v>0.1312</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9389</v>
+        <v>9390</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33701</v>
+        <v>33702</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8493</v>
+        <v>8486</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10116</v>
+        <v>10118</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51968</v>
+        <v>51980</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51962</v>
+        <v>51980</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52177</v>
+        <v>52178</v>
       </c>
       <c r="F52" t="n">
         <v>0.0498</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50948</v>
+        <v>50954</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50969</v>
+        <v>50975</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52198</v>
+        <v>52199</v>
       </c>
       <c r="F77" t="n">
         <v>0.0498</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52951</v>
+        <v>52944</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52915</v>
+        <v>52907</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:49</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53213</v>
+        <v>53224</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52065</v>
+        <v>52053</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0497</v>
+        <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54528</v>
+        <v>54508</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:50</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52183</v>
+        <v>52177</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53040</v>
+        <v>53018</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51951</v>
+        <v>51952</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54601</v>
+        <v>54605</v>
       </c>
       <c r="F182" t="n">
         <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53746</v>
+        <v>53639</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53188</v>
+        <v>53217</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:19</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53082</v>
+        <v>53075</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52908</v>
+        <v>52920</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52888</v>
+        <v>52902</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52825</v>
+        <v>52817</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52883</v>
+        <v>52885</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52646</v>
+        <v>52653</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52920</v>
+        <v>52918</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52886</v>
+        <v>52890</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52853</v>
+        <v>52745</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0504</v>
+        <v>0.0503</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53089</v>
+        <v>53084</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52995</v>
+        <v>52986</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52838</v>
+        <v>52865</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53108</v>
+        <v>53132</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0506</v>
+        <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53997</v>
+        <v>54011</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85033</v>
+        <v>85035</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27225</v>
+        <v>27230</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:51</t>
+          <t>2026-09-15 14:38:20</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5817</v>
+        <v>5820</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F221" t="n">
         <v>0.0011</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F222" t="n">
         <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F233" t="n">
         <v>0.0011</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F234" t="n">
         <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5817</v>
+        <v>5820</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5983</v>
+        <v>5982</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:17</t>
+          <t>2026-09-15 14:35:27</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:48</t>
+          <t>2026-09-15 14:38:17</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5941</v>
+        <v>5939</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5887</v>
+        <v>5889</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5898</v>
+        <v>5896</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:15</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1352</v>
+        <v>1332</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5923</v>
+        <v>5920</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5958</v>
+        <v>5957</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16480,14 +16480,14 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F487" t="n">
         <v>0.0012</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5997</v>
+        <v>5999</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16810,14 +16810,14 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F497" t="n">
         <v>0.0012</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16876,14 +16876,14 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F499" t="n">
         <v>0.0012</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17008,14 +17008,14 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1239</v>
+        <v>1230</v>
       </c>
       <c r="F503" t="n">
         <v>0.0012</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>6017</v>
+        <v>5991</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17404,14 +17404,14 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="F515" t="n">
         <v>0.0012</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17536,14 +17536,14 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F519" t="n">
         <v>0.0013</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-14 16:08:47</t>
+          <t>2026-09-15 14:38:16</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17088</v>
+        <v>17065</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:36</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56069</v>
+        <v>56046</v>
       </c>
       <c r="F522" t="n">
-        <v>0.0535</v>
+        <v>0.0534</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:36</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17668,14 +17668,14 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>31009</v>
+        <v>31003</v>
       </c>
       <c r="F523" t="n">
         <v>0.0296</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:36</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19040</v>
+        <v>19028</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:36</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133381</v>
+        <v>133358</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:36</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427193</v>
+        <v>427170</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23564</v>
+        <v>23595</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60843</v>
+        <v>60828</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4568</v>
+        <v>4565</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5568</v>
+        <v>5557</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-14 16:06:37</t>
+          <t>2026-09-15 14:35:42</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17285</v>
+        <v>17310</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:01</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81096</v>
+        <v>81105</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:01</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38409</v>
+        <v>38441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0366</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:01</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19467</v>
+        <v>19451</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0186</v>
+        <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:01</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>173891</v>
+        <v>174257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1658</v>
+        <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:01</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>470325</v>
+        <v>471243</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4485</v>
+        <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15243</v>
+        <v>15967</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0145</v>
+        <v>0.0152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56032</v>
+        <v>56132</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0534</v>
+        <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8651</v>
+        <v>8652</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5297</v>
+        <v>5283</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6370</v>
+        <v>6368</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-15 14:36:02</t>
+          <t>2026-09-16 14:32:49</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79611</v>
+        <v>79637</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442953</v>
+        <v>442963</v>
       </c>
       <c r="F43" t="n">
         <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137528</v>
+        <v>137560</v>
       </c>
       <c r="F44" t="n">
         <v>0.1312</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70402</v>
+        <v>70398</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9390</v>
+        <v>9394</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33702</v>
+        <v>33706</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8486</v>
+        <v>8466</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10118</v>
+        <v>10083</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51980</v>
+        <v>51988</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50954</v>
+        <v>50953</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50975</v>
+        <v>50974</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2389,14 +2389,14 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>50374</v>
+        <v>51202</v>
       </c>
       <c r="F60" t="n">
-        <v>0.048</v>
+        <v>0.0488</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2422,14 +2422,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>50277</v>
+        <v>51118</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0479</v>
+        <v>0.0487</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52944</v>
+        <v>52955</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52907</v>
+        <v>52909</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>50419</v>
+        <v>51259</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0481</v>
+        <v>0.0489</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -3082,14 +3082,14 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>50359</v>
+        <v>51144</v>
       </c>
       <c r="F81" t="n">
-        <v>0.048</v>
+        <v>0.0488</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:45</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:18</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:46</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53224</v>
+        <v>53229</v>
       </c>
       <c r="F175" t="n">
         <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52053</v>
+        <v>52059</v>
       </c>
       <c r="F176" t="n">
         <v>0.0496</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54508</v>
+        <v>54504</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52177</v>
+        <v>52181</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53018</v>
+        <v>53038</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53078</v>
+        <v>53068</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51952</v>
+        <v>51950</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54605</v>
+        <v>54601</v>
       </c>
       <c r="F182" t="n">
         <v>0.0521</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53639</v>
+        <v>53647</v>
       </c>
       <c r="F183" t="n">
         <v>0.0512</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53217</v>
+        <v>53206</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0508</v>
+        <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:19</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52920</v>
+        <v>52918</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52902</v>
+        <v>52904</v>
       </c>
       <c r="F187" t="n">
         <v>0.0505</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52819</v>
+        <v>52818</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52817</v>
+        <v>52823</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52885</v>
+        <v>52877</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52653</v>
+        <v>52651</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52918</v>
+        <v>52917</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52890</v>
+        <v>52887</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52745</v>
+        <v>52743</v>
       </c>
       <c r="F194" t="n">
         <v>0.0503</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53084</v>
+        <v>53092</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52880</v>
+        <v>52893</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52865</v>
+        <v>52862</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52328</v>
+        <v>52339</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>54011</v>
+        <v>54001</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:42</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27230</v>
+        <v>27237</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14913</v>
+        <v>14908</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:20</t>
+          <t>2026-09-16 14:35:47</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10424</v>
+        <v>10415</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F217" t="n">
         <v>0.0011</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5820</v>
+        <v>5817</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0055</v>
+        <v>0.0056</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1217</v>
+        <v>1235</v>
       </c>
       <c r="F235" t="n">
         <v>0.0012</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8197,14 +8197,14 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5941</v>
+        <v>5955</v>
       </c>
       <c r="F236" t="n">
         <v>0.0057</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8230,14 +8230,14 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1215</v>
+        <v>1230</v>
       </c>
       <c r="F237" t="n">
         <v>0.0012</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8263,14 +8263,14 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5902</v>
+        <v>5909</v>
       </c>
       <c r="F238" t="n">
         <v>0.0056</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5820</v>
+        <v>5817</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5972</v>
+        <v>5977</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9484,14 +9484,14 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1183</v>
+        <v>1203</v>
       </c>
       <c r="F275" t="n">
         <v>0.0011</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9517,14 +9517,14 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5937</v>
+        <v>5953</v>
       </c>
       <c r="F276" t="n">
         <v>0.0057</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9550,14 +9550,14 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1167</v>
+        <v>1187</v>
       </c>
       <c r="F277" t="n">
         <v>0.0011</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5919</v>
+        <v>5915</v>
       </c>
       <c r="F278" t="n">
         <v>0.0056</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:27</t>
+          <t>2026-09-16 14:31:40</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:17</t>
+          <t>2026-09-16 14:35:44</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5889</v>
+        <v>5888</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5896</v>
+        <v>5899</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:15</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16084,14 +16084,14 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F475" t="n">
         <v>0.0012</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5827</v>
+        <v>5826</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6080</v>
+        <v>6079</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5920</v>
+        <v>5917</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5957</v>
+        <v>5959</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5999</v>
+        <v>5997</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5999</v>
+        <v>5998</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16744,14 +16744,14 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="F495" t="n">
         <v>0.0012</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16876,14 +16876,14 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F499" t="n">
         <v>0.0012</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16942,14 +16942,14 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F501" t="n">
         <v>0.0012</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17041,14 +17041,14 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>5991</v>
+        <v>5990</v>
       </c>
       <c r="F504" t="n">
         <v>0.0057</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17470,14 +17470,14 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F517" t="n">
         <v>0.0011</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="F520" t="n">
         <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-15 14:38:16</t>
+          <t>2026-09-16 14:35:43</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17065</v>
+        <v>17066</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56046</v>
+        <v>56047</v>
       </c>
       <c r="F522" t="n">
-        <v>0.0534</v>
+        <v>0.0535</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19028</v>
+        <v>19032</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133358</v>
+        <v>133359</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427170</v>
+        <v>427171</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23595</v>
+        <v>23591</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60828</v>
+        <v>60825</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3306</v>
+        <v>3308</v>
       </c>
       <c r="F534" t="n">
         <v>0.0032</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5557</v>
+        <v>5554</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35:42</t>
+          <t>2026-09-16 14:31:55</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17310</v>
+        <v>17311</v>
       </c>
       <c r="F2" t="n">
         <v>0.0165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81105</v>
+        <v>81106</v>
       </c>
       <c r="F3" t="n">
         <v>0.07729999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19451</v>
+        <v>19449</v>
       </c>
       <c r="F5" t="n">
         <v>0.0185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174257</v>
+        <v>174258</v>
       </c>
       <c r="F6" t="n">
         <v>0.1662</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471243</v>
+        <v>471244</v>
       </c>
       <c r="F7" t="n">
         <v>0.4494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56132</v>
+        <v>56135</v>
       </c>
       <c r="F9" t="n">
         <v>0.0535</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="F14" t="n">
         <v>0.002</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8652</v>
+        <v>8653</v>
       </c>
       <c r="F15" t="n">
         <v>0.0083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5283</v>
+        <v>5286</v>
       </c>
       <c r="F16" t="n">
         <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6368</v>
+        <v>6364</v>
       </c>
       <c r="F17" t="n">
         <v>0.0061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-16 14:32:49</t>
+          <t>2026-09-17 14:36:15</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79637</v>
+        <v>79630</v>
       </c>
       <c r="F42" t="n">
         <v>0.0759</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442963</v>
+        <v>442956</v>
       </c>
       <c r="F43" t="n">
         <v>0.4224</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70398</v>
+        <v>70400</v>
       </c>
       <c r="F45" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9394</v>
+        <v>9387</v>
       </c>
       <c r="F46" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33706</v>
+        <v>33699</v>
       </c>
       <c r="F47" t="n">
         <v>0.0321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8466</v>
+        <v>8449</v>
       </c>
       <c r="F48" t="n">
         <v>0.0081</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10083</v>
+        <v>10100</v>
       </c>
       <c r="F49" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51988</v>
+        <v>51978</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51980</v>
+        <v>51984</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52178</v>
+        <v>52176</v>
       </c>
       <c r="F52" t="n">
         <v>0.0498</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2158,14 +2158,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>50953</v>
+        <v>50952</v>
       </c>
       <c r="F53" t="n">
         <v>0.0486</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2323,14 +2323,14 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48455</v>
+        <v>48441</v>
       </c>
       <c r="F58" t="n">
         <v>0.0462</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50974</v>
+        <v>50973</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>50620</v>
+        <v>50630</v>
       </c>
       <c r="F76" t="n">
         <v>0.0483</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,14 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>52199</v>
+        <v>52197</v>
       </c>
       <c r="F77" t="n">
         <v>0.0498</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52955</v>
+        <v>52954</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52909</v>
+        <v>52907</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:45</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:48</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:46</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52059</v>
+        <v>52065</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54504</v>
+        <v>54510</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52181</v>
+        <v>52185</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53038</v>
+        <v>53006</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53068</v>
+        <v>53074</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51950</v>
+        <v>51942</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54601</v>
+        <v>54576</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0521</v>
+        <v>0.052</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6448,14 +6448,14 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>53647</v>
+        <v>53605</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0512</v>
+        <v>0.0511</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53206</v>
+        <v>53214</v>
       </c>
       <c r="F184" t="n">
         <v>0.0507</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53075</v>
+        <v>53077</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52918</v>
+        <v>52916</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52904</v>
+        <v>52899</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0505</v>
+        <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52818</v>
+        <v>52821</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52823</v>
+        <v>52826</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52877</v>
+        <v>52870</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52651</v>
+        <v>52650</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52917</v>
+        <v>52927</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:49</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52887</v>
+        <v>52884</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52743</v>
+        <v>52748</v>
       </c>
       <c r="F194" t="n">
         <v>0.0503</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53092</v>
+        <v>53084</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53079</v>
+        <v>53076</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52986</v>
+        <v>52994</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6943,14 +6943,14 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>52893</v>
+        <v>52891</v>
       </c>
       <c r="F198" t="n">
         <v>0.0504</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52862</v>
+        <v>52847</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53132</v>
+        <v>53137</v>
       </c>
       <c r="F200" t="n">
         <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7042,14 +7042,14 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>52339</v>
+        <v>52333</v>
       </c>
       <c r="F201" t="n">
         <v>0.0499</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>54001</v>
+        <v>53999</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:42</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85035</v>
+        <v>85036</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27237</v>
+        <v>27211</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7339,14 +7339,14 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>14908</v>
+        <v>14907</v>
       </c>
       <c r="F210" t="n">
         <v>0.0142</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:47</t>
+          <t>2026-09-17 14:39:50</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10415</v>
+        <v>10416</v>
       </c>
       <c r="F212" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7570,14 +7570,14 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F217" t="n">
         <v>0.0011</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5883</v>
+        <v>5885</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5817</v>
+        <v>5816</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F221" t="n">
         <v>0.0011</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5820</v>
+        <v>5817</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8032,14 +8032,14 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="F231" t="n">
         <v>0.0009</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8098,14 +8098,14 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F233" t="n">
         <v>0.0011</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8131,14 +8131,14 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5820</v>
+        <v>5817</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0056</v>
+        <v>0.0055</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9220,14 +9220,14 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F267" t="n">
         <v>0.001</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9253,14 +9253,14 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="F268" t="n">
         <v>0.0054</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9319,14 +9319,14 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5817</v>
+        <v>5816</v>
       </c>
       <c r="F270" t="n">
         <v>0.0055</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9385,14 +9385,14 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5977</v>
+        <v>5973</v>
       </c>
       <c r="F272" t="n">
         <v>0.0057</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5982</v>
+        <v>5980</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6416</v>
+        <v>6417</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6189</v>
+        <v>6190</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6141</v>
+        <v>6142</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6399</v>
+        <v>6400</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6351</v>
+        <v>6352</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5277</v>
+        <v>5278</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6401</v>
+        <v>6402</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6341</v>
+        <v>6342</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6387</v>
+        <v>6388</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6052</v>
+        <v>6050</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:40</t>
+          <t>2026-09-17 14:35:23</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6408</v>
+        <v>6409</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5682</v>
+        <v>5683</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6418</v>
+        <v>6419</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6329</v>
+        <v>6330</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6324</v>
+        <v>6325</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6424</v>
+        <v>6425</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6470</v>
+        <v>6471</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6436</v>
+        <v>6437</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6437</v>
+        <v>6438</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6383</v>
+        <v>6384</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6395</v>
+        <v>6396</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5004</v>
+        <v>5005</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>4999</v>
+        <v>5000</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6446</v>
+        <v>6447</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6470</v>
+        <v>6471</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6256</v>
+        <v>6257</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6220</v>
+        <v>6221</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:44</t>
+          <t>2026-09-17 14:39:47</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15853,14 +15853,14 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5869</v>
+        <v>5870</v>
       </c>
       <c r="F468" t="n">
         <v>0.0056</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5899</v>
+        <v>5896</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16084,14 +16084,14 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F475" t="n">
         <v>0.0012</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5826</v>
+        <v>5828</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6079</v>
+        <v>6076</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16282,14 +16282,14 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F481" t="n">
         <v>0.0013</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16315,14 +16315,14 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5917</v>
+        <v>5916</v>
       </c>
       <c r="F482" t="n">
         <v>0.0056</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16381,14 +16381,14 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5959</v>
+        <v>5957</v>
       </c>
       <c r="F484" t="n">
         <v>0.0057</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5994</v>
+        <v>5993</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16645,14 +16645,14 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>5998</v>
+        <v>5997</v>
       </c>
       <c r="F492" t="n">
         <v>0.0057</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5972</v>
+        <v>5971</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16744,14 +16744,14 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F495" t="n">
         <v>0.0012</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16909,14 +16909,14 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="F500" t="n">
         <v>0.0057</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6017</v>
+        <v>6016</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17107,14 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="F506" t="n">
         <v>0.0058</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17239,14 +17239,14 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6014</v>
+        <v>6012</v>
       </c>
       <c r="F510" t="n">
         <v>0.0057</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17272,14 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F511" t="n">
         <v>0.0012</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17305,14 +17305,14 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>6018</v>
+        <v>6020</v>
       </c>
       <c r="F512" t="n">
         <v>0.0057</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17470,14 +17470,14 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F517" t="n">
         <v>0.0011</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="F520" t="n">
         <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-16 14:35:43</t>
+          <t>2026-09-17 14:39:46</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17066</v>
+        <v>17058</v>
       </c>
       <c r="F521" t="n">
         <v>0.0163</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56047</v>
+        <v>56039</v>
       </c>
       <c r="F522" t="n">
-        <v>0.0535</v>
+        <v>0.0534</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19032</v>
+        <v>19027</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0182</v>
+        <v>0.0181</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133359</v>
+        <v>133351</v>
       </c>
       <c r="F525" t="n">
         <v>0.1272</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427171</v>
+        <v>427163</v>
       </c>
       <c r="F526" t="n">
         <v>0.4074</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23591</v>
+        <v>23553</v>
       </c>
       <c r="F527" t="n">
         <v>0.0225</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60825</v>
+        <v>60822</v>
       </c>
       <c r="F528" t="n">
         <v>0.058</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="F533" t="n">
         <v>0.0008</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3308</v>
+        <v>3299</v>
       </c>
       <c r="F534" t="n">
-        <v>0.0032</v>
+        <v>0.0031</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4565</v>
+        <v>4562</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>
@@ -18097,14 +18097,14 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>5554</v>
+        <v>5551</v>
       </c>
       <c r="F536" t="n">
         <v>0.0053</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31:55</t>
+          <t>2026-09-17 14:35:41</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17311</v>
+        <v>13707</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0165</v>
+        <v>0.0131</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81106</v>
+        <v>64181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38441</v>
+        <v>30520</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0367</v>
+        <v>0.0291</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19449</v>
+        <v>16666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0185</v>
+        <v>0.0159</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>174258</v>
+        <v>136732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1662</v>
+        <v>0.1304</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>471244</v>
+        <v>367754</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4494</v>
+        <v>0.3507</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15967</v>
+        <v>15022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0152</v>
+        <v>0.0143</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56135</v>
+        <v>44984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0535</v>
+        <v>0.0429</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2139</v>
+        <v>1688</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002</v>
+        <v>0.0016</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8653</v>
+        <v>6738</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0083</v>
+        <v>0.0064</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5286</v>
+        <v>5113</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0.0049</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6364</v>
+        <v>6104</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0061</v>
+        <v>0.0058</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:15</t>
+          <t>2026-09-18 14:04:48</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>79630</v>
+        <v>74913</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0759</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>442956</v>
+        <v>415262</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4224</v>
+        <v>0.396</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>137560</v>
+        <v>128083</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1312</v>
+        <v>0.1221</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70400</v>
+        <v>66393</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9387</v>
+        <v>8713</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33699</v>
+        <v>31269</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0321</v>
+        <v>0.0298</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8449</v>
+        <v>8295</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0081</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10100</v>
+        <v>9796</v>
       </c>
       <c r="F49" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51978</v>
+        <v>51988</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51984</v>
+        <v>51980</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52176</v>
+        <v>52179</v>
       </c>
       <c r="F52" t="n">
         <v>0.0498</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -2983,14 +2983,14 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>52954</v>
+        <v>52956</v>
       </c>
       <c r="F78" t="n">
         <v>0.0505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>52907</v>
+        <v>52911</v>
       </c>
       <c r="F79" t="n">
         <v>0.0505</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:48</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>53229</v>
+        <v>53227</v>
       </c>
       <c r="F175" t="n">
         <v>0.0508</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6250,14 +6250,14 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>54510</v>
+        <v>54511</v>
       </c>
       <c r="F177" t="n">
         <v>0.052</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6283,14 +6283,14 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>52185</v>
+        <v>52181</v>
       </c>
       <c r="F178" t="n">
         <v>0.0498</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6316,14 +6316,14 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53006</v>
+        <v>53036</v>
       </c>
       <c r="F179" t="n">
         <v>0.0506</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6349,14 +6349,14 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>53074</v>
+        <v>53058</v>
       </c>
       <c r="F180" t="n">
         <v>0.0506</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6382,14 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>51942</v>
+        <v>51953</v>
       </c>
       <c r="F181" t="n">
         <v>0.0495</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6415,14 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>54576</v>
+        <v>54575</v>
       </c>
       <c r="F182" t="n">
         <v>0.052</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6481,14 +6481,14 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>53214</v>
+        <v>53219</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0507</v>
+        <v>0.0508</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>53077</v>
+        <v>53062</v>
       </c>
       <c r="F185" t="n">
         <v>0.0506</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6547,14 +6547,14 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>52916</v>
+        <v>52912</v>
       </c>
       <c r="F186" t="n">
         <v>0.0505</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>52899</v>
+        <v>52900</v>
       </c>
       <c r="F187" t="n">
         <v>0.0504</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6613,14 +6613,14 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>52821</v>
+        <v>52820</v>
       </c>
       <c r="F188" t="n">
         <v>0.0504</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>52826</v>
+        <v>52830</v>
       </c>
       <c r="F189" t="n">
         <v>0.0504</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6679,14 +6679,14 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>52870</v>
+        <v>52883</v>
       </c>
       <c r="F190" t="n">
         <v>0.0504</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6712,14 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>52650</v>
+        <v>52653</v>
       </c>
       <c r="F191" t="n">
         <v>0.0502</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>52927</v>
+        <v>52912</v>
       </c>
       <c r="F192" t="n">
         <v>0.0505</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:49</t>
+          <t>2026-09-18 14:08:13</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>52884</v>
+        <v>52886</v>
       </c>
       <c r="F193" t="n">
         <v>0.0504</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6811,14 +6811,14 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>52748</v>
+        <v>52750</v>
       </c>
       <c r="F194" t="n">
         <v>0.0503</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>53084</v>
+        <v>53064</v>
       </c>
       <c r="F195" t="n">
         <v>0.0506</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6877,14 +6877,14 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>53076</v>
+        <v>53073</v>
       </c>
       <c r="F196" t="n">
         <v>0.0506</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6910,14 +6910,14 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52994</v>
+        <v>52992</v>
       </c>
       <c r="F197" t="n">
         <v>0.0505</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>52847</v>
+        <v>52838</v>
       </c>
       <c r="F199" t="n">
         <v>0.0504</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7009,14 +7009,14 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53137</v>
+        <v>53126</v>
       </c>
       <c r="F200" t="n">
         <v>0.0507</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7075,14 +7075,14 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>53999</v>
+        <v>54001</v>
       </c>
       <c r="F202" t="n">
         <v>0.0515</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7240,14 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>85036</v>
+        <v>85035</v>
       </c>
       <c r="F207" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7273,14 +7273,14 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>27211</v>
+        <v>27257</v>
       </c>
       <c r="F208" t="n">
         <v>0.026</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:50</t>
+          <t>2026-09-18 14:08:14</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20560</v>
+        <v>18925</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0196</v>
+        <v>0.018</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>10416</v>
+        <v>9997</v>
       </c>
       <c r="F212" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0095</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:12</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7504,14 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F215" t="n">
         <v>0.0011</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7603,14 +7603,14 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5885</v>
+        <v>5884</v>
       </c>
       <c r="F218" t="n">
         <v>0.0056</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7636,14 +7636,14 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F219" t="n">
         <v>0.0012</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5816</v>
+        <v>5818</v>
       </c>
       <c r="F220" t="n">
         <v>0.0055</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -7702,14 +7702,14 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F221" t="n">
         <v>0.0011</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9451,14 +9451,14 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="F274" t="n">
         <v>0.0057</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -9979,14 +9979,14 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="F290" t="n">
         <v>0.0061</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10045,14 +10045,14 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6190</v>
+        <v>6189</v>
       </c>
       <c r="F292" t="n">
         <v>0.0059</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10111,14 +10111,14 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6142</v>
+        <v>6141</v>
       </c>
       <c r="F294" t="n">
         <v>0.0059</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10177,14 +10177,14 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6400</v>
+        <v>6399</v>
       </c>
       <c r="F296" t="n">
         <v>0.0061</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10243,14 +10243,14 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6352</v>
+        <v>6351</v>
       </c>
       <c r="F298" t="n">
         <v>0.0061</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10309,14 +10309,14 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5310</v>
+        <v>5309</v>
       </c>
       <c r="F300" t="n">
         <v>0.0051</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10375,14 +10375,14 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>5278</v>
+        <v>5277</v>
       </c>
       <c r="F302" t="n">
         <v>0.005</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10441,14 +10441,14 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6402</v>
+        <v>6401</v>
       </c>
       <c r="F304" t="n">
         <v>0.0061</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10507,14 +10507,14 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6342</v>
+        <v>6341</v>
       </c>
       <c r="F306" t="n">
         <v>0.006</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10573,14 +10573,14 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6300</v>
+        <v>6299</v>
       </c>
       <c r="F308" t="n">
         <v>0.006</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10639,14 +10639,14 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="F310" t="n">
         <v>0.006</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10705,14 +10705,14 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6388</v>
+        <v>6387</v>
       </c>
       <c r="F312" t="n">
         <v>0.0061</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10771,14 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6401</v>
+        <v>6400</v>
       </c>
       <c r="F314" t="n">
         <v>0.0061</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10837,14 +10837,14 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="F316" t="n">
         <v>0.0058</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10903,14 +10903,14 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5993</v>
+        <v>5992</v>
       </c>
       <c r="F318" t="n">
         <v>0.0057</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:23</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14203,14 +14203,14 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>6387</v>
+        <v>6386</v>
       </c>
       <c r="F418" t="n">
         <v>0.0061</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14269,14 +14269,14 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6409</v>
+        <v>6408</v>
       </c>
       <c r="F420" t="n">
         <v>0.0061</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14335,14 +14335,14 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5683</v>
+        <v>5682</v>
       </c>
       <c r="F422" t="n">
         <v>0.0054</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14401,14 +14401,14 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>5647</v>
+        <v>5646</v>
       </c>
       <c r="F424" t="n">
         <v>0.0054</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14467,14 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6391</v>
+        <v>6390</v>
       </c>
       <c r="F426" t="n">
         <v>0.0061</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14533,14 +14533,14 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6419</v>
+        <v>6418</v>
       </c>
       <c r="F428" t="n">
         <v>0.0061</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6330</v>
+        <v>6329</v>
       </c>
       <c r="F430" t="n">
         <v>0.006</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14665,14 +14665,14 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6325</v>
+        <v>6324</v>
       </c>
       <c r="F432" t="n">
         <v>0.006</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14731,14 +14731,14 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6425</v>
+        <v>6424</v>
       </c>
       <c r="F434" t="n">
         <v>0.0061</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14797,14 +14797,14 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>6471</v>
+        <v>6470</v>
       </c>
       <c r="F436" t="n">
         <v>0.0062</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14863,14 +14863,14 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>5948</v>
+        <v>5947</v>
       </c>
       <c r="F438" t="n">
         <v>0.0057</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14929,14 +14929,14 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="F440" t="n">
         <v>0.0056</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -14995,14 +14995,14 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>6437</v>
+        <v>6436</v>
       </c>
       <c r="F442" t="n">
         <v>0.0061</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15061,14 +15061,14 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6438</v>
+        <v>6437</v>
       </c>
       <c r="F444" t="n">
         <v>0.0061</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15127,14 +15127,14 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6392</v>
+        <v>6391</v>
       </c>
       <c r="F446" t="n">
         <v>0.0061</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15193,14 +15193,14 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6408</v>
+        <v>6407</v>
       </c>
       <c r="F448" t="n">
         <v>0.0061</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15259,14 +15259,14 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6384</v>
+        <v>6383</v>
       </c>
       <c r="F450" t="n">
         <v>0.0061</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15325,14 +15325,14 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>6396</v>
+        <v>6395</v>
       </c>
       <c r="F452" t="n">
         <v>0.0061</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15391,14 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5005</v>
+        <v>5004</v>
       </c>
       <c r="F454" t="n">
         <v>0.0048</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15457,14 +15457,14 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>5000</v>
+        <v>4999</v>
       </c>
       <c r="F456" t="n">
         <v>0.0048</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15523,14 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>6447</v>
+        <v>6446</v>
       </c>
       <c r="F458" t="n">
         <v>0.0061</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15589,14 +15589,14 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6471</v>
+        <v>6470</v>
       </c>
       <c r="F460" t="n">
         <v>0.0062</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15655,14 +15655,14 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>6257</v>
+        <v>6256</v>
       </c>
       <c r="F462" t="n">
         <v>0.006</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15721,14 +15721,14 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="F464" t="n">
         <v>0.0059</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:47</t>
+          <t>2026-09-18 14:08:11</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -15787,14 +15787,14 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5939</v>
+        <v>5936</v>
       </c>
       <c r="F466" t="n">
         <v>0.0057</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -15919,14 +15919,14 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6069</v>
+        <v>6068</v>
       </c>
       <c r="F470" t="n">
         <v>0.0058</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -15985,14 +15985,14 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5889</v>
+        <v>5888</v>
       </c>
       <c r="F472" t="n">
         <v>0.0056</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -16018,14 +16018,14 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="F473" t="n">
         <v>0.0012</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -16051,14 +16051,14 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>5896</v>
+        <v>5898</v>
       </c>
       <c r="F474" t="n">
         <v>0.0056</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>5925</v>
+        <v>5923</v>
       </c>
       <c r="F476" t="n">
-        <v>0.0057</v>
+        <v>0.0056</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -16150,14 +16150,14 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F477" t="n">
         <v>0.001</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16183,14 +16183,14 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5828</v>
+        <v>5827</v>
       </c>
       <c r="F478" t="n">
         <v>0.0056</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16249,14 +16249,14 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="F480" t="n">
         <v>0.0058</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16414,14 +16414,14 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F485" t="n">
         <v>0.0012</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16447,14 +16447,14 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="F486" t="n">
         <v>0.0057</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16513,14 +16513,14 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="F488" t="n">
         <v>0.0057</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16579,14 +16579,14 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="F490" t="n">
         <v>0.0057</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16711,14 +16711,14 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="F494" t="n">
         <v>0.0057</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16744,14 +16744,14 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F495" t="n">
         <v>0.0012</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16777,14 +16777,14 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="F496" t="n">
         <v>0.0057</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16810,14 +16810,14 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F497" t="n">
         <v>0.0012</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16843,14 +16843,14 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>5994</v>
+        <v>5992</v>
       </c>
       <c r="F498" t="n">
         <v>0.0057</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -16975,14 +16975,14 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="F502" t="n">
         <v>0.0057</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17074,14 +17074,14 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F505" t="n">
         <v>0.0012</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17140,14 +17140,14 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F507" t="n">
         <v>0.0012</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17173,14 +17173,14 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="F508" t="n">
         <v>0.0057</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17371,14 +17371,14 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="F514" t="n">
         <v>0.0057</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17437,14 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="F516" t="n">
         <v>0.0056</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:01:58</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:09</t>
         </is>
       </c>
     </row>
@@ -17569,14 +17569,14 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="F520" t="n">
         <v>0.0058</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-09-17 14:39:46</t>
+          <t>2026-09-18 14:08:10</t>
         </is>
       </c>
     </row>
@@ -17602,14 +17602,14 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>17058</v>
+        <v>16169</v>
       </c>
       <c r="F521" t="n">
-        <v>0.0163</v>
+        <v>0.0154</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17635,14 +17635,14 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>56039</v>
+        <v>55634</v>
       </c>
       <c r="F522" t="n">
-        <v>0.0534</v>
+        <v>0.0531</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17668,14 +17668,14 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>31003</v>
+        <v>29977</v>
       </c>
       <c r="F523" t="n">
-        <v>0.0296</v>
+        <v>0.0286</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17701,14 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>19027</v>
+        <v>18638</v>
       </c>
       <c r="F524" t="n">
-        <v>0.0181</v>
+        <v>0.0178</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17734,14 +17734,14 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>133351</v>
+        <v>125081</v>
       </c>
       <c r="F525" t="n">
-        <v>0.1272</v>
+        <v>0.1193</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17767,14 +17767,14 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>427163</v>
+        <v>397905</v>
       </c>
       <c r="F526" t="n">
-        <v>0.4074</v>
+        <v>0.3795</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17800,14 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>23553</v>
+        <v>22657</v>
       </c>
       <c r="F527" t="n">
-        <v>0.0225</v>
+        <v>0.0216</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17833,14 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>60822</v>
+        <v>56984</v>
       </c>
       <c r="F528" t="n">
-        <v>0.058</v>
+        <v>0.0543</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -17998,14 +17998,14 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>811</v>
+        <v>782</v>
       </c>
       <c r="F533" t="n">
-        <v>0.0008</v>
+        <v>0.0007</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -18031,14 +18031,14 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3299</v>
+        <v>3256</v>
       </c>
       <c r="F534" t="n">
         <v>0.0031</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -18064,14 +18064,14 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4562</v>
+        <v>4570</v>
       </c>
       <c r="F535" t="n">
         <v>0.0044</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35:41</t>
+          <t>2026-09-18 14:02:17</t>
         </is>
       </c>
     </row>

--- a/data/final/documentacao/lista_arquivos_disponiveis.xlsx
+++ b/data/final/documentacao/lista_arquivos_disponiveis.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13707</v>
+        <v>16166</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0131</v>
+        <v>0.0154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64181</v>
+        <v>77279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0612</v>
+        <v>0.0737</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30520</v>
+        <v>36238</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0291</v>
+        <v>0.0346</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16666</v>
+        <v>18449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0159</v>
+        <v>0.0176</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>136732</v>
+        <v>163305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1304</v>
+        <v>0.1557</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>367754</v>
+        <v>444007</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3507</v>
+        <v>0.4234</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15022</v>
+        <v>14823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0143</v>
+        <v>0.0141</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>44984</v>
+        <v>53199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0429</v>
+        <v>0.0507</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1688</v>
+        <v>2034</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6738</v>
+        <v>8182</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0064</v>
+        <v>0.0078</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5113</v>
+        <v>5254</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6104</v>
+        <v>6303</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0058</v>
+        <v>0.006</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:04:48</t>
+          <t>2026-09-19 13:39:28</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:53</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:53</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:53</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:53</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:53</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:01:58</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>74913</v>
+        <v>78426</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>415262</v>
+        <v>436750</v>
       </c>
       <c r="F43" t="n">
-        <v>0.396</v>
+        <v>0.4165</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>128083</v>
+        <v>135224</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1221</v>
+        <v>0.129</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>66393</v>
+        <v>69110</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0633</v>
+        <v>0.0659</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8713</v>
+        <v>9243</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0083</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31269</v>
+        <v>33123</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0298</v>
+        <v>0.0316</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -1993,14 +1993,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8295</v>
+        <v>8415</v>
       </c>
       <c r="F48" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -2026,14 +2026,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9796</v>
+        <v>10014</v>
       </c>
       <c r="F49" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:09</t>
+          <t>2026-09-19 13:41:54</t>
         </is>
       </c>
     </row>
@@ -2059,14 +2059,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51988</v>
+        <v>51990</v>
       </c>
       <c r="F50" t="n">
         <v>0.0496</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51980</v>
+        <v>51982</v>
       </c>
       <c r="F51" t="n">
         <v>0.0496</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50973</v>
+        <v>50978</v>
       </c>
       <c r="F59" t="n">
         <v>0.0486</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:08:12</t>
+          <t>2026-09-19 13:41:55</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G72" t="inlineStr">
     